--- a/public/assets/files/SISB_Data_Start.xlsx
+++ b/public/assets/files/SISB_Data_Start.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/genevieve_guex_epfl_ch/Documents/Documents/SISB_Presentations/SISB-Apero-Slidev/public/assets/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="460" documentId="8_{D825BCA8-78DA-496A-9FDB-1D07E1398520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DC4D394-761E-4960-8990-04AC384FF277}"/>
+  <xr:revisionPtr revIDLastSave="571" documentId="8_{D825BCA8-78DA-496A-9FDB-1D07E1398520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F21624EE-3DB2-4957-A35E-7FD82DE7DB68}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="6765" windowWidth="27990" windowHeight="14220" firstSheet="1" activeTab="2" xr2:uid="{8AE9B5FF-3248-49A6-BDC7-A12E71D01EE7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="7" xr2:uid="{8AE9B5FF-3248-49A6-BDC7-A12E71D01EE7}"/>
   </bookViews>
   <sheets>
     <sheet name="Entrées" sheetId="2" r:id="rId1"/>
-    <sheet name="SISB_Data_2026" sheetId="1" r:id="rId2"/>
-    <sheet name="SISB_Data_2026 (2)" sheetId="10" r:id="rId3"/>
+    <sheet name="SISB_Data_2026" sheetId="10" r:id="rId2"/>
+    <sheet name="SISB_Data_Stats_2026" sheetId="1" r:id="rId3"/>
     <sheet name="&gt;&gt; Fichier final" sheetId="5" r:id="rId4"/>
     <sheet name="SISB_Data_Stats_Formules" sheetId="8" r:id="rId5"/>
     <sheet name="SISB_Data_Viz" sheetId="9" r:id="rId6"/>
     <sheet name="&gt;&gt; Guides" sheetId="3" r:id="rId7"/>
     <sheet name="Theme EPFL" sheetId="7" r:id="rId8"/>
+    <sheet name="Références" sheetId="11" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
     <definedName name="DateDebut" localSheetId="4">SISB_Data_Stats_Formules!$C$11</definedName>
@@ -109,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="76">
   <si>
     <t>Jour</t>
   </si>
@@ -305,6 +306,39 @@
   <si>
     <t>453A4C</t>
   </si>
+  <si>
+    <t xml:space="preserve">Original Tyrannosaurus by Alberto Cairo, 2016 </t>
+  </si>
+  <si>
+    <t>Same Stats, Different Graphs</t>
+  </si>
+  <si>
+    <t>Download dataset</t>
+  </si>
+  <si>
+    <t>The Datasaurus Dozen Dataset</t>
+  </si>
+  <si>
+    <t>C:\Users\[NOM UTILISATEUR]AppData\Roaming\Microsoft\Templates\Document Themes</t>
+  </si>
+  <si>
+    <t>Thèmes pour Excel</t>
+  </si>
+  <si>
+    <t>Télécharger les thèmes</t>
+  </si>
+  <si>
+    <t>Viridis</t>
+  </si>
+  <si>
+    <t>EPFL</t>
+  </si>
+  <si>
+    <t>Viridis Mako</t>
+  </si>
+  <si>
+    <t>Viridis Rocket</t>
+  </si>
 </sst>
 </file>
 
@@ -314,7 +348,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="9"/>
       <color theme="1"/>
@@ -401,8 +435,21 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="10"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -517,6 +564,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -571,11 +624,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -697,14 +751,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -922,6 +976,105 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-CH">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Aptos SemiBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>Evolution du nombre d'</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="fr-CH">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos SemiBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>entrées</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="fr-CH">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Aptos SemiBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t> et de </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="fr-CH">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos SemiBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>prêts</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="fr-CH">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Aptos SemiBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t> physiques à la Bibliothèque</a:t>
+            </a:r>
+            <a:br>
+              <a:rPr lang="fr-CH">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
+            </a:br>
+            <a:r>
+              <a:rPr lang="fr-CH" sz="1000">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>01.01.2026..23.05.2026</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="1.3275612318126734E-2"/>
+          <c:y val="1.8462513586423219E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -930,39 +1083,29 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.3558248953396143E-2"/>
+          <c:y val="0.1588864705793637"/>
+          <c:w val="0.92861554292224247"/>
+          <c:h val="0.70346563444963095"/>
+        </c:manualLayout>
+      </c:layout>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="4"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>SISB_Data_2026!$B$6</c:f>
+              <c:f>SISB_Data_Stats_Formules!$B$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -972,20 +1115,18 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="22225">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SISB_Data_2026!$C$5:$EN$5</c:f>
+              <c:f>SISB_Data_Stats_Formules!$C$5:$EN$5</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="142"/>
@@ -1420,7 +1561,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SISB_Data_2026!$C$6:$EN$6</c:f>
+              <c:f>SISB_Data_Stats_Formules!$C$6:$EN$6</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="142"/>
@@ -1856,16 +1997,16 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A792-47E6-8A2B-1BB4A2486C89}"/>
+              <c16:uniqueId val="{00000000-D2BA-4CE0-84B7-B994431F9344}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
+          <c:idx val="5"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>SISB_Data_2026!$B$7</c:f>
+              <c:f>SISB_Data_Stats_Formules!$B$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1875,20 +2016,18 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="22225">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SISB_Data_2026!$C$5:$EN$5</c:f>
+              <c:f>SISB_Data_Stats_Formules!$C$5:$EN$5</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="142"/>
@@ -2323,7 +2462,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SISB_Data_2026!$C$7:$EN$7</c:f>
+              <c:f>SISB_Data_Stats_Formules!$C$7:$EN$7</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="142"/>
@@ -2759,7 +2898,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A792-47E6-8A2B-1BB4A2486C89}"/>
+              <c16:uniqueId val="{00000001-D2BA-4CE0-84B7-B994431F9344}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2772,11 +2911,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="579518223"/>
-        <c:axId val="1531787151"/>
+        <c:axId val="1384193808"/>
+        <c:axId val="697417168"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="579518223"/>
+        <c:axId val="1384193808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2791,8 +2930,7 @@
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
+                <a:lumMod val="50000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -2805,10 +2943,12 @@
           <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
                 <a:solidFill>
                   <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                    <a:lumMod val="50000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -2819,41 +2959,33 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1531787151"/>
+        <c:crossAx val="697417168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="1"/>
+        <c:majorTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="1531787151"/>
+        <c:axId val="697417168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="0" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
           <a:ln>
-            <a:noFill/>
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -2865,8 +2997,7 @@
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                    <a:lumMod val="50000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -2877,74 +3008,27 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="579518223"/>
+        <c:crossAx val="1384193808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
+        <a:ln w="25400">
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
+    <c:extLst/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
-    <a:effectLst/>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -3104,7 +3188,7 @@
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="4"/>
+          <c:idx val="2"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
@@ -3118,7 +3202,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="22225">
+            <a:ln w="19050">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
@@ -4000,12 +4084,12 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D2BA-4CE0-84B7-B994431F9344}"/>
+              <c16:uniqueId val="{00000010-F598-402B-8F05-6C36C84FD6C9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="5"/>
+          <c:idx val="3"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
@@ -4019,7 +4103,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="22225">
+            <a:ln w="19050">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -4028,6 +4112,15 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="78"/>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000016-F598-402B-8F05-6C36C84FD6C9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:cat>
             <c:numRef>
               <c:f>SISB_Data_Stats_Formules!$C$5:$EN$5</c:f>
@@ -4901,7 +4994,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D2BA-4CE0-84B7-B994431F9344}"/>
+              <c16:uniqueId val="{00000011-F598-402B-8F05-6C36C84FD6C9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5017,7 +5110,7 @@
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="25400">
+        <a:ln w="6350">
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
@@ -5187,2102 +5280,6 @@
           <c:h val="0.70346563444963095"/>
         </c:manualLayout>
       </c:layout>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>SISB_Data_Stats_Formules!$B$6</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Entrées physiques</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>SISB_Data_Stats_Formules!$C$5:$EN$5</c:f>
-              <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="142"/>
-                <c:pt idx="0">
-                  <c:v>46023</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>46024</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>46025</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>46026</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>46027</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>46028</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>46029</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>46030</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>46031</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>46032</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>46033</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>46034</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>46035</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>46036</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>46037</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>46038</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>46039</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>46040</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>46041</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>46042</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>46043</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>46044</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>46045</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>46046</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>46047</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>46048</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>46049</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>46050</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>46051</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>46052</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>46053</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>46054</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>46055</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>46056</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>46057</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>46058</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>46059</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>46060</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>46061</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>46062</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>46063</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>46064</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>46065</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>46066</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>46067</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>46068</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>46069</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>46070</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>46071</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>46072</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>46073</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>46074</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>46075</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>46076</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>46077</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>46078</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>46079</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>46080</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>46081</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>46082</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>46083</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>46084</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>46085</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>46086</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>46087</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>46088</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>46089</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>46090</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>46091</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>46092</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>46093</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>46094</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>46095</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>46096</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>46097</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>46098</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>46099</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>46100</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>46101</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>46102</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>46103</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>46104</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>46105</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>46106</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>46107</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>46108</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>46109</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>46110</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>46111</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>46112</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>46113</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>46114</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>46115</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>46116</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>46117</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>46118</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>46119</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>46120</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>46121</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>46122</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>46123</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>46124</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>46125</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>46126</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>46127</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>46128</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>46129</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>46130</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>46131</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>46132</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>46133</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>46134</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>46135</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>46136</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>46137</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>46138</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>46139</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>46140</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>46141</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>46142</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>46143</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>46144</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>46145</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>46146</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>46147</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>46148</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>46149</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>46150</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>46151</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>46152</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>46153</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>46154</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>46155</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>46156</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>46157</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>46158</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>46159</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>46160</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>46161</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>46162</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>46163</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>46164</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>SISB_Data_Stats_Formules!$C$6:$EN$6</c:f>
-              <c:numCache>
-                <c:formatCode>0</c:formatCode>
-                <c:ptCount val="142"/>
-                <c:pt idx="0">
-                  <c:v>553.846</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>515.38499999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>461.53799999999995</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>428.20500000000004</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>407.69200000000001</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>387.17899999999997</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>356.40999999999997</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>330.76900000000001</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>289.74399999999997</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>261.53800000000001</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>230.76899999999998</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>223.077</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>223.077</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>233.33300000000003</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>258.97399999999999</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>294.87200000000001</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>328.20500000000004</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>353.846</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>402.56399999999996</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>441.02600000000001</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>466.66699999999997</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>500</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>530.76900000000001</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>566.66700000000003</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>592.30799999999999</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>612.82100000000003</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>615.38499999999999</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>617.94899999999996</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>574.35899999999992</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>548.71799999999996</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>525.64100000000008</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>482.05100000000004</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>494.87200000000001</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>510.25599999999997</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>453.846</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>428.20500000000004</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>387.17899999999997</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>351.28199999999998</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>325.64100000000002</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>300</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>335.89699999999999</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>366.66699999999997</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>382.05100000000004</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>297.43600000000004</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>297.43600000000004</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>300</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>320.51299999999998</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>358.97399999999999</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>410.25599999999997</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>441.02600000000001</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>471.79499999999996</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>494.87200000000001</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>515.38499999999999</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>535.89700000000005</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>551.28200000000004</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>566.66700000000003</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>592.30799999999999</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>623.077</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>648.71799999999996</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>679.48700000000008</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>705.12799999999993</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>715.38499999999999</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>715.38499999999999</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>694.87200000000007</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>469.23099999999999</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>482.05100000000004</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>500</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>530.76900000000001</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>553.846</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>566.66700000000003</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>561.53800000000001</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>538.46199999999999</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>512.82100000000003</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>500</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>479.48700000000002</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>297.43600000000004</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>297.43600000000004</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>312.82100000000003</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>579.48700000000008</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>617.94899999999996</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>648.71799999999996</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>684.61500000000001</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>707.69200000000001</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>720.51299999999992</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>738.46199999999999</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>751.28200000000004</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>766.66700000000003</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>776.923</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>797.43600000000004</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>817.94899999999996</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>833.33299999999997</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>851.28200000000004</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>864.10300000000007</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>879.48700000000008</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>894.87200000000007</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>933.33299999999997</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>953.846</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>982.05100000000004</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>566.66700000000003</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>592.30799999999999</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>607.69200000000001</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>630.76900000000001</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>641.02599999999995</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>643.58999999999992</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>743.58999999999992</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>712.82100000000003</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>679.48700000000008</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>658.97400000000005</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>630.76900000000001</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>612.82100000000003</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>587.17899999999997</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>551.28200000000004</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>523.077</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>497.43600000000004</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>474.35899999999998</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>448.71800000000002</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>487.17899999999997</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>512.82100000000003</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>541.02600000000007</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>561.53800000000001</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>520.51299999999992</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>487.17899999999997</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>471.79499999999996</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>461.53799999999995</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>505.12799999999999</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>538.46199999999999</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>574.35899999999992</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>600</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>641.02599999999995</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>669.23099999999999</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>712.82100000000003</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>743.58999999999992</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>782.05100000000004</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>679.48700000000008</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>684.61500000000001</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>682.05100000000004</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>376.923</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>394.87200000000001</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>912.82100000000003</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>500</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>479.48700000000002</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>441.02600000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000010-F598-402B-8F05-6C36C84FD6C9}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>SISB_Data_Stats_Formules!$B$7</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Prêts physiques</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dPt>
-            <c:idx val="78"/>
-            <c:bubble3D val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000016-F598-402B-8F05-6C36C84FD6C9}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:cat>
-            <c:numRef>
-              <c:f>SISB_Data_Stats_Formules!$C$5:$EN$5</c:f>
-              <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="142"/>
-                <c:pt idx="0">
-                  <c:v>46023</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>46024</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>46025</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>46026</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>46027</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>46028</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>46029</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>46030</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>46031</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>46032</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>46033</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>46034</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>46035</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>46036</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>46037</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>46038</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>46039</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>46040</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>46041</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>46042</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>46043</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>46044</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>46045</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>46046</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>46047</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>46048</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>46049</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>46050</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>46051</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>46052</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>46053</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>46054</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>46055</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>46056</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>46057</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>46058</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>46059</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>46060</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>46061</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>46062</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>46063</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>46064</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>46065</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>46066</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>46067</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>46068</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>46069</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>46070</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>46071</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>46072</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>46073</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>46074</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>46075</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>46076</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>46077</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>46078</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>46079</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>46080</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>46081</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>46082</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>46083</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>46084</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>46085</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>46086</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>46087</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>46088</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>46089</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>46090</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>46091</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>46092</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>46093</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>46094</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>46095</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>46096</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>46097</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>46098</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>46099</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>46100</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>46101</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>46102</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>46103</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>46104</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>46105</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>46106</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>46107</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>46108</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>46109</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>46110</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>46111</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>46112</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>46113</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>46114</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>46115</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>46116</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>46117</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>46118</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>46119</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>46120</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>46121</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>46122</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>46123</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>46124</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>46125</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>46126</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>46127</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>46128</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>46129</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>46130</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>46131</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>46132</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>46133</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>46134</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>46135</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>46136</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>46137</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>46138</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>46139</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>46140</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>46141</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>46142</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>46143</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>46144</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>46145</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>46146</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>46147</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>46148</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>46149</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>46150</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>46151</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>46152</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>46153</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>46154</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>46155</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>46156</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>46157</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>46158</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>46159</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>46160</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>46161</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>46162</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>46163</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>46164</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>SISB_Data_Stats_Formules!$C$7:$EN$7</c:f>
-              <c:numCache>
-                <c:formatCode>0</c:formatCode>
-                <c:ptCount val="142"/>
-                <c:pt idx="0">
-                  <c:v>971.79500000000007</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>960.25599999999997</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>944.87200000000007</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>914.10300000000007</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>883.33299999999997</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>848.71799999999996</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>798.71799999999996</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>775.64099999999996</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>744.87200000000007</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>714.10300000000007</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>664.10300000000007</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>617.94899999999996</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>571.79499999999996</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>529.48700000000008</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>510.25599999999997</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>510.25599999999997</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>510.25599999999997</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>514.10299999999995</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>514.10299999999995</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>529.48700000000008</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>541.02600000000007</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>552.56399999999996</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>556.41</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>560.25599999999997</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>579.48700000000008</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>621.79499999999996</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>664.10300000000007</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>691.02599999999995</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>552.56399999999996</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>498.71800000000002</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>460.25599999999997</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>383.33300000000003</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>421.79499999999996</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>441.02600000000001</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>364.10300000000001</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>325.64100000000002</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>314.10300000000001</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>302.56399999999996</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>321.79499999999996</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>367.94899999999996</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>414.10300000000001</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>456.40999999999997</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>491.02600000000001</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>360.25599999999997</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>321.79499999999996</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>291.02600000000001</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>267.94899999999996</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>252.56399999999999</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>252.56399999999999</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>256.40999999999997</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>287.18</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>314.10300000000001</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>348.71800000000002</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>375.64100000000002</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>406.40999999999997</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>421.79499999999996</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>444.87200000000001</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>460.25599999999997</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>467.94899999999996</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>479.48700000000002</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>537.18000000000006</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>606.41</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>644.87200000000007</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>694.87200000000007</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>798.71799999999996</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>841.02599999999995</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>852.56399999999996</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>852.56399999999996</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>860.25599999999997</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>860.25599999999997</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>829.48700000000008</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>806.41000000000008</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>787.18000000000006</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>787.18000000000006</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>775.64099999999996</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>598.71799999999996</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>621.79499999999996</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>625.64100000000008</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>994.87200000000007</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>991.02599999999995</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>975.64099999999996</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>941.02599999999995</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>910.25599999999997</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>864.10300000000007</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>833.33299999999997</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>791.02599999999995</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>752.56399999999996</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>714.10300000000007</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>667.94899999999996</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>602.56399999999996</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>552.56399999999996</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>514.10299999999995</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>475.64100000000002</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>460.25599999999997</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>425.64100000000002</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>398.71800000000002</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>367.94899999999996</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>337.18000000000006</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>406.40999999999997</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>383.33300000000003</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>337.18000000000006</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>291.02600000000001</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>252.56399999999999</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>241.02599999999998</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>229.48699999999999</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>229.48699999999999</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>221.79500000000002</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>202.56399999999999</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>191.02599999999998</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>191.02599999999998</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>183.33300000000003</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>183.33300000000003</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>183.33300000000003</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>175.64099999999999</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>160.256</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>137.18</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>148.71800000000002</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>148.71800000000002</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>148.71800000000002</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>141.02600000000001</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>125.64099999999999</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>110.256</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>98.718000000000004</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>60.256</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>94.872</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>102.56399999999999</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>102.56399999999999</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>106.41</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>106.41</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>106.41</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>106.41</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>106.41</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>106.41</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>87.18</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>52.564</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>29.487000000000002</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>257.69200000000001</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>253.846</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>415.38499999999999</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>957.69200000000001</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>950</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>926.923</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000011-F598-402B-8F05-6C36C84FD6C9}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="1384193808"/>
-        <c:axId val="697417168"/>
-      </c:lineChart>
-      <c:dateAx>
-        <c:axId val="1384193808"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="697417168"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblOffset val="100"/>
-        <c:baseTimeUnit val="days"/>
-        <c:majorUnit val="1"/>
-        <c:majorTimeUnit val="months"/>
-      </c:dateAx>
-      <c:valAx>
-        <c:axId val="697417168"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="0" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1384193808"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="6350">
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst/>
-  </c:chart>
-  <c:spPr>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="fr-FR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l">
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="fr-CH">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Aptos SemiBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t>Evolution du nombre d'</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="fr-CH">
-                <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
-                </a:solidFill>
-                <a:latin typeface="Aptos SemiBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t>entrées</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="fr-CH">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Aptos SemiBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t> et de </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="fr-CH">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:latin typeface="Aptos SemiBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t>prêts</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="fr-CH">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Aptos SemiBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t> physiques à la Bibliothèque</a:t>
-            </a:r>
-            <a:br>
-              <a:rPr lang="fr-CH">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:rPr>
-            </a:br>
-            <a:r>
-              <a:rPr lang="fr-CH" sz="1000">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>01.01.2026..23.05.2026</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="1.3275612318126734E-2"/>
-          <c:y val="1.8462513586423219E-2"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="5.3558248953396143E-2"/>
-          <c:y val="0.1588864705793637"/>
-          <c:w val="0.92861554292224247"/>
-          <c:h val="0.70346563444963095"/>
-        </c:manualLayout>
-      </c:layout>
       <c:areaChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -9235,7 +7232,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -10434,46 +8431,6 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -11030,522 +8987,6 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -12094,42 +9535,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>413658</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>141515</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>299358</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>114301</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Graphique 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EA03035-F909-19B9-3C4E-A1839214DC24}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -12766,8 +10171,8 @@
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>32842</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>647</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>79088</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -12810,8 +10215,8 @@
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>501017</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>13518</xdr:rowOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>91960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -12836,6 +10241,875 @@
         <a:xfrm>
           <a:off x="7469350" y="3476543"/>
           <a:ext cx="7367726" cy="7429093"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>425823</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>212912</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>546433</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>77704</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{138853BA-F917-ECAC-19C8-BD8FDC709E5F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17324294" y="2924736"/>
+          <a:ext cx="3314286" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>397811</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>263339</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>599516</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>308163</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Flèche : bas 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F31F7EAA-03BD-4633-06CF-936183C22A53}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="15167965">
+          <a:off x="16741590" y="3518648"/>
+          <a:ext cx="672353" cy="840441"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="fr-CH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>129989</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>219637</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>163607</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>118784</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Flèche : bas 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CF65E4F-7E5A-4C00-980D-CC85F189E6FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="1639176">
+          <a:off x="20222136" y="2303931"/>
+          <a:ext cx="672353" cy="840441"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="fr-CH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>453838</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>61631</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>16808</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>106454</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Flèche : bas 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6575ECCE-BC81-4B8B-8021-3B448A3A25C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="16797617" y="7866528"/>
+          <a:ext cx="672353" cy="840441"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="fr-CH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>403411</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>40340</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>298077</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Graphique 8" descr="Badge 1 avec un remplissage uni">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{495309D5-9626-3215-19DF-041A7EDF7948}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId5"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20495558" y="1467971"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>228441</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>93971</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>504106</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>67077</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Graphique 10" descr="Badge avec un remplissage uni">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AB14156-9E73-7887-DE87-F5BEC5033628}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId7"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15849441" y="3747089"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>199146</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>109500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>474811</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>82606</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Graphique 12" descr="Badge 3 avec un remplissage uni">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0C46A26-6D68-77AC-C866-B3BACD6821BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId9"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15820146" y="7920000"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>1591235</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>56029</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>2039470</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>268940</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Flèche : bas 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C309855-7818-7CBF-2030-89BF87AD91F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="23599588" y="3395382"/>
+          <a:ext cx="448235" cy="526676"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="fr-CH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>2028265</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>224117</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5132294" cy="311496"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="ZoneTexte 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5A5690D-9DA6-BB7E-CDCD-49A47BDAEC67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24036618" y="3563470"/>
+          <a:ext cx="5132294" cy="311496"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="fr-CH" sz="1400">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>première lettre de votre prénom puis</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="fr-CH" sz="1400" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> votre nom sans espace</a:t>
+          </a:r>
+          <a:endParaRPr lang="fr-CH" sz="1400">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>134470</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>246196</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>140107</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Image 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E082D05-1109-F78C-9B32-75ED392CC73F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="25168411" y="5614147"/>
+          <a:ext cx="2666667" cy="4219048"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>33617</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>2700284</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>140107</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Image 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C03005C1-CBCC-5A77-BC4B-8449DF65C1B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22041970" y="5614147"/>
+          <a:ext cx="2666667" cy="4219048"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>67234</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>178960</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>140107</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Image 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35EC1CCB-0695-3276-473F-13DB03C10DA2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="28294852" y="5614147"/>
+          <a:ext cx="2666667" cy="4219048"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>111726</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>140107</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Image 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BECBFF58-CAF3-49D9-0497-88312F532704}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31421294" y="5614147"/>
+          <a:ext cx="2666667" cy="4219048"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>582706</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>569982</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>96138</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Image 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79589A00-100C-B30E-8455-89D10D9F1542}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17481177" y="9334500"/>
+          <a:ext cx="3180952" cy="1866667"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>240926</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>28013</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>442632</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>72837</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Flèche : bas 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEE0C693-DFCA-45D2-9CE0-1458613E2B1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="17223441" y="9480175"/>
+          <a:ext cx="672353" cy="840441"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="fr-CH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>593912</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>56029</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>230841</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>29135</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Graphique 22" descr="Badge 4 avec un remplissage uni">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A009D5A6-7F44-C7AC-AC63-781E3654F627}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId16"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16214912" y="9435353"/>
+          <a:ext cx="914400" cy="914400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12883,24 +11157,28 @@
 </externalLink>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="GGU-EPFL">
   <a:themeElements>
-    <a:clrScheme name="EPFL-SISB-Officiel">
+    <a:clrScheme name="Personnalisé 7">
       <a:dk1>
-        <a:srgbClr val="413C3A"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
         <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="413C3A"/>
+        <a:srgbClr val="413D3A"/>
       </a:dk2>
       <a:lt2>
         <a:srgbClr val="CAC7C7"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="E30613"/>
+        <a:srgbClr val="FF0000"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="00A79F"/>
@@ -14640,1480 +12918,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02763E32-D334-407F-8BF3-222AB88B5A7C}">
-  <dimension ref="A1:EN41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="9.1640625" style="52" customWidth="1"/>
-    <col min="2" max="2" width="35.5" style="52" customWidth="1"/>
-    <col min="3" max="144" width="11.6640625" style="52" bestFit="1" customWidth="1"/>
-    <col min="145" max="16384" width="11.1640625" style="52"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:144" ht="91.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:144" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B2" s="64" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="2:144" x14ac:dyDescent="0.2">
-      <c r="B3" s="52" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="2:144" s="67" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="65" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="66">
-        <v>46023</v>
-      </c>
-      <c r="D5" s="66">
-        <v>46024</v>
-      </c>
-      <c r="E5" s="66">
-        <v>46025</v>
-      </c>
-      <c r="F5" s="66">
-        <v>46026</v>
-      </c>
-      <c r="G5" s="66">
-        <v>46027</v>
-      </c>
-      <c r="H5" s="66">
-        <v>46028</v>
-      </c>
-      <c r="I5" s="66">
-        <v>46029</v>
-      </c>
-      <c r="J5" s="66">
-        <v>46030</v>
-      </c>
-      <c r="K5" s="66">
-        <v>46031</v>
-      </c>
-      <c r="L5" s="66">
-        <v>46032</v>
-      </c>
-      <c r="M5" s="66">
-        <v>46033</v>
-      </c>
-      <c r="N5" s="66">
-        <v>46034</v>
-      </c>
-      <c r="O5" s="66">
-        <v>46035</v>
-      </c>
-      <c r="P5" s="66">
-        <v>46036</v>
-      </c>
-      <c r="Q5" s="66">
-        <v>46037</v>
-      </c>
-      <c r="R5" s="66">
-        <v>46038</v>
-      </c>
-      <c r="S5" s="66">
-        <v>46039</v>
-      </c>
-      <c r="T5" s="66">
-        <v>46040</v>
-      </c>
-      <c r="U5" s="66">
-        <v>46041</v>
-      </c>
-      <c r="V5" s="66">
-        <v>46042</v>
-      </c>
-      <c r="W5" s="66">
-        <v>46043</v>
-      </c>
-      <c r="X5" s="66">
-        <v>46044</v>
-      </c>
-      <c r="Y5" s="66">
-        <v>46045</v>
-      </c>
-      <c r="Z5" s="66">
-        <v>46046</v>
-      </c>
-      <c r="AA5" s="66">
-        <v>46047</v>
-      </c>
-      <c r="AB5" s="66">
-        <v>46048</v>
-      </c>
-      <c r="AC5" s="66">
-        <v>46049</v>
-      </c>
-      <c r="AD5" s="66">
-        <v>46050</v>
-      </c>
-      <c r="AE5" s="66">
-        <v>46051</v>
-      </c>
-      <c r="AF5" s="66">
-        <v>46052</v>
-      </c>
-      <c r="AG5" s="66">
-        <v>46053</v>
-      </c>
-      <c r="AH5" s="66">
-        <v>46054</v>
-      </c>
-      <c r="AI5" s="66">
-        <v>46055</v>
-      </c>
-      <c r="AJ5" s="66">
-        <v>46056</v>
-      </c>
-      <c r="AK5" s="66">
-        <v>46057</v>
-      </c>
-      <c r="AL5" s="66">
-        <v>46058</v>
-      </c>
-      <c r="AM5" s="66">
-        <v>46059</v>
-      </c>
-      <c r="AN5" s="66">
-        <v>46060</v>
-      </c>
-      <c r="AO5" s="66">
-        <v>46061</v>
-      </c>
-      <c r="AP5" s="66">
-        <v>46062</v>
-      </c>
-      <c r="AQ5" s="66">
-        <v>46063</v>
-      </c>
-      <c r="AR5" s="66">
-        <v>46064</v>
-      </c>
-      <c r="AS5" s="66">
-        <v>46065</v>
-      </c>
-      <c r="AT5" s="66">
-        <v>46066</v>
-      </c>
-      <c r="AU5" s="66">
-        <v>46067</v>
-      </c>
-      <c r="AV5" s="66">
-        <v>46068</v>
-      </c>
-      <c r="AW5" s="66">
-        <v>46069</v>
-      </c>
-      <c r="AX5" s="66">
-        <v>46070</v>
-      </c>
-      <c r="AY5" s="66">
-        <v>46071</v>
-      </c>
-      <c r="AZ5" s="66">
-        <v>46072</v>
-      </c>
-      <c r="BA5" s="66">
-        <v>46073</v>
-      </c>
-      <c r="BB5" s="66">
-        <v>46074</v>
-      </c>
-      <c r="BC5" s="66">
-        <v>46075</v>
-      </c>
-      <c r="BD5" s="66">
-        <v>46076</v>
-      </c>
-      <c r="BE5" s="66">
-        <v>46077</v>
-      </c>
-      <c r="BF5" s="66">
-        <v>46078</v>
-      </c>
-      <c r="BG5" s="66">
-        <v>46079</v>
-      </c>
-      <c r="BH5" s="66">
-        <v>46080</v>
-      </c>
-      <c r="BI5" s="66">
-        <v>46081</v>
-      </c>
-      <c r="BJ5" s="66">
-        <v>46082</v>
-      </c>
-      <c r="BK5" s="66">
-        <v>46083</v>
-      </c>
-      <c r="BL5" s="66">
-        <v>46084</v>
-      </c>
-      <c r="BM5" s="66">
-        <v>46085</v>
-      </c>
-      <c r="BN5" s="66">
-        <v>46086</v>
-      </c>
-      <c r="BO5" s="66">
-        <v>46087</v>
-      </c>
-      <c r="BP5" s="66">
-        <v>46088</v>
-      </c>
-      <c r="BQ5" s="66">
-        <v>46089</v>
-      </c>
-      <c r="BR5" s="66">
-        <v>46090</v>
-      </c>
-      <c r="BS5" s="66">
-        <v>46091</v>
-      </c>
-      <c r="BT5" s="66">
-        <v>46092</v>
-      </c>
-      <c r="BU5" s="66">
-        <v>46093</v>
-      </c>
-      <c r="BV5" s="66">
-        <v>46094</v>
-      </c>
-      <c r="BW5" s="66">
-        <v>46095</v>
-      </c>
-      <c r="BX5" s="66">
-        <v>46096</v>
-      </c>
-      <c r="BY5" s="66">
-        <v>46097</v>
-      </c>
-      <c r="BZ5" s="66">
-        <v>46098</v>
-      </c>
-      <c r="CA5" s="66">
-        <v>46099</v>
-      </c>
-      <c r="CB5" s="66">
-        <v>46100</v>
-      </c>
-      <c r="CC5" s="66">
-        <v>46101</v>
-      </c>
-      <c r="CD5" s="66">
-        <v>46102</v>
-      </c>
-      <c r="CE5" s="66">
-        <v>46103</v>
-      </c>
-      <c r="CF5" s="66">
-        <v>46104</v>
-      </c>
-      <c r="CG5" s="66">
-        <v>46105</v>
-      </c>
-      <c r="CH5" s="66">
-        <v>46106</v>
-      </c>
-      <c r="CI5" s="66">
-        <v>46107</v>
-      </c>
-      <c r="CJ5" s="66">
-        <v>46108</v>
-      </c>
-      <c r="CK5" s="66">
-        <v>46109</v>
-      </c>
-      <c r="CL5" s="66">
-        <v>46110</v>
-      </c>
-      <c r="CM5" s="66">
-        <v>46111</v>
-      </c>
-      <c r="CN5" s="66">
-        <v>46112</v>
-      </c>
-      <c r="CO5" s="66">
-        <v>46113</v>
-      </c>
-      <c r="CP5" s="66">
-        <v>46114</v>
-      </c>
-      <c r="CQ5" s="66">
-        <v>46115</v>
-      </c>
-      <c r="CR5" s="66">
-        <v>46116</v>
-      </c>
-      <c r="CS5" s="66">
-        <v>46117</v>
-      </c>
-      <c r="CT5" s="66">
-        <v>46118</v>
-      </c>
-      <c r="CU5" s="66">
-        <v>46119</v>
-      </c>
-      <c r="CV5" s="66">
-        <v>46120</v>
-      </c>
-      <c r="CW5" s="66">
-        <v>46121</v>
-      </c>
-      <c r="CX5" s="66">
-        <v>46122</v>
-      </c>
-      <c r="CY5" s="66">
-        <v>46123</v>
-      </c>
-      <c r="CZ5" s="66">
-        <v>46124</v>
-      </c>
-      <c r="DA5" s="66">
-        <v>46125</v>
-      </c>
-      <c r="DB5" s="66">
-        <v>46126</v>
-      </c>
-      <c r="DC5" s="66">
-        <v>46127</v>
-      </c>
-      <c r="DD5" s="66">
-        <v>46128</v>
-      </c>
-      <c r="DE5" s="66">
-        <v>46129</v>
-      </c>
-      <c r="DF5" s="66">
-        <v>46130</v>
-      </c>
-      <c r="DG5" s="66">
-        <v>46131</v>
-      </c>
-      <c r="DH5" s="66">
-        <v>46132</v>
-      </c>
-      <c r="DI5" s="66">
-        <v>46133</v>
-      </c>
-      <c r="DJ5" s="66">
-        <v>46134</v>
-      </c>
-      <c r="DK5" s="66">
-        <v>46135</v>
-      </c>
-      <c r="DL5" s="66">
-        <v>46136</v>
-      </c>
-      <c r="DM5" s="66">
-        <v>46137</v>
-      </c>
-      <c r="DN5" s="66">
-        <v>46138</v>
-      </c>
-      <c r="DO5" s="66">
-        <v>46139</v>
-      </c>
-      <c r="DP5" s="66">
-        <v>46140</v>
-      </c>
-      <c r="DQ5" s="66">
-        <v>46141</v>
-      </c>
-      <c r="DR5" s="66">
-        <v>46142</v>
-      </c>
-      <c r="DS5" s="66">
-        <v>46143</v>
-      </c>
-      <c r="DT5" s="66">
-        <v>46144</v>
-      </c>
-      <c r="DU5" s="66">
-        <v>46145</v>
-      </c>
-      <c r="DV5" s="66">
-        <v>46146</v>
-      </c>
-      <c r="DW5" s="66">
-        <v>46147</v>
-      </c>
-      <c r="DX5" s="66">
-        <v>46148</v>
-      </c>
-      <c r="DY5" s="66">
-        <v>46149</v>
-      </c>
-      <c r="DZ5" s="66">
-        <v>46150</v>
-      </c>
-      <c r="EA5" s="66">
-        <v>46151</v>
-      </c>
-      <c r="EB5" s="66">
-        <v>46152</v>
-      </c>
-      <c r="EC5" s="66">
-        <v>46153</v>
-      </c>
-      <c r="ED5" s="66">
-        <v>46154</v>
-      </c>
-      <c r="EE5" s="66">
-        <v>46155</v>
-      </c>
-      <c r="EF5" s="66">
-        <v>46156</v>
-      </c>
-      <c r="EG5" s="66">
-        <v>46157</v>
-      </c>
-      <c r="EH5" s="66">
-        <v>46158</v>
-      </c>
-      <c r="EI5" s="66">
-        <v>46159</v>
-      </c>
-      <c r="EJ5" s="66">
-        <v>46160</v>
-      </c>
-      <c r="EK5" s="66">
-        <v>46161</v>
-      </c>
-      <c r="EL5" s="66">
-        <v>46162</v>
-      </c>
-      <c r="EM5" s="66">
-        <v>46163</v>
-      </c>
-      <c r="EN5" s="66">
-        <v>46164</v>
-      </c>
-    </row>
-    <row r="6" spans="2:144" x14ac:dyDescent="0.2">
-      <c r="B6" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="69">
-        <v>553.846</v>
-      </c>
-      <c r="D6" s="69">
-        <v>515.38499999999999</v>
-      </c>
-      <c r="E6" s="69">
-        <v>461.53799999999995</v>
-      </c>
-      <c r="F6" s="69">
-        <v>428.20500000000004</v>
-      </c>
-      <c r="G6" s="69">
-        <v>407.69200000000001</v>
-      </c>
-      <c r="H6" s="69">
-        <v>387.17899999999997</v>
-      </c>
-      <c r="I6" s="69">
-        <v>356.40999999999997</v>
-      </c>
-      <c r="J6" s="69">
-        <v>330.76900000000001</v>
-      </c>
-      <c r="K6" s="69">
-        <v>289.74399999999997</v>
-      </c>
-      <c r="L6" s="69">
-        <v>261.53800000000001</v>
-      </c>
-      <c r="M6" s="69">
-        <v>230.76899999999998</v>
-      </c>
-      <c r="N6" s="69">
-        <v>223.077</v>
-      </c>
-      <c r="O6" s="69">
-        <v>223.077</v>
-      </c>
-      <c r="P6" s="69">
-        <v>233.33300000000003</v>
-      </c>
-      <c r="Q6" s="69">
-        <v>258.97399999999999</v>
-      </c>
-      <c r="R6" s="69">
-        <v>294.87200000000001</v>
-      </c>
-      <c r="S6" s="69">
-        <v>328.20500000000004</v>
-      </c>
-      <c r="T6" s="69">
-        <v>353.846</v>
-      </c>
-      <c r="U6" s="69">
-        <v>402.56399999999996</v>
-      </c>
-      <c r="V6" s="69">
-        <v>441.02600000000001</v>
-      </c>
-      <c r="W6" s="69">
-        <v>466.66699999999997</v>
-      </c>
-      <c r="X6" s="69">
-        <v>500</v>
-      </c>
-      <c r="Y6" s="69">
-        <v>530.76900000000001</v>
-      </c>
-      <c r="Z6" s="69">
-        <v>566.66700000000003</v>
-      </c>
-      <c r="AA6" s="69">
-        <v>592.30799999999999</v>
-      </c>
-      <c r="AB6" s="69">
-        <v>612.82100000000003</v>
-      </c>
-      <c r="AC6" s="69">
-        <v>615.38499999999999</v>
-      </c>
-      <c r="AD6" s="69">
-        <v>617.94899999999996</v>
-      </c>
-      <c r="AE6" s="69">
-        <v>574.35899999999992</v>
-      </c>
-      <c r="AF6" s="69">
-        <v>548.71799999999996</v>
-      </c>
-      <c r="AG6" s="69">
-        <v>525.64100000000008</v>
-      </c>
-      <c r="AH6" s="69">
-        <v>482.05100000000004</v>
-      </c>
-      <c r="AI6" s="69">
-        <v>494.87200000000001</v>
-      </c>
-      <c r="AJ6" s="69">
-        <v>510.25599999999997</v>
-      </c>
-      <c r="AK6" s="69">
-        <v>453.846</v>
-      </c>
-      <c r="AL6" s="69">
-        <v>428.20500000000004</v>
-      </c>
-      <c r="AM6" s="69">
-        <v>387.17899999999997</v>
-      </c>
-      <c r="AN6" s="69">
-        <v>351.28199999999998</v>
-      </c>
-      <c r="AO6" s="69">
-        <v>325.64100000000002</v>
-      </c>
-      <c r="AP6" s="69">
-        <v>300</v>
-      </c>
-      <c r="AQ6" s="69">
-        <v>335.89699999999999</v>
-      </c>
-      <c r="AR6" s="69">
-        <v>366.66699999999997</v>
-      </c>
-      <c r="AS6" s="69">
-        <v>382.05100000000004</v>
-      </c>
-      <c r="AT6" s="69">
-        <v>297.43600000000004</v>
-      </c>
-      <c r="AU6" s="69">
-        <v>297.43600000000004</v>
-      </c>
-      <c r="AV6" s="69">
-        <v>300</v>
-      </c>
-      <c r="AW6" s="69">
-        <v>320.51299999999998</v>
-      </c>
-      <c r="AX6" s="69">
-        <v>358.97399999999999</v>
-      </c>
-      <c r="AY6" s="69">
-        <v>410.25599999999997</v>
-      </c>
-      <c r="AZ6" s="69">
-        <v>441.02600000000001</v>
-      </c>
-      <c r="BA6" s="69">
-        <v>471.79499999999996</v>
-      </c>
-      <c r="BB6" s="69">
-        <v>494.87200000000001</v>
-      </c>
-      <c r="BC6" s="69">
-        <v>515.38499999999999</v>
-      </c>
-      <c r="BD6" s="69">
-        <v>535.89700000000005</v>
-      </c>
-      <c r="BE6" s="69">
-        <v>551.28200000000004</v>
-      </c>
-      <c r="BF6" s="69">
-        <v>566.66700000000003</v>
-      </c>
-      <c r="BG6" s="69">
-        <v>592.30799999999999</v>
-      </c>
-      <c r="BH6" s="69">
-        <v>623.077</v>
-      </c>
-      <c r="BI6" s="69">
-        <v>648.71799999999996</v>
-      </c>
-      <c r="BJ6" s="69">
-        <v>679.48700000000008</v>
-      </c>
-      <c r="BK6" s="69">
-        <v>705.12799999999993</v>
-      </c>
-      <c r="BL6" s="69">
-        <v>715.38499999999999</v>
-      </c>
-      <c r="BM6" s="69">
-        <v>715.38499999999999</v>
-      </c>
-      <c r="BN6" s="69">
-        <v>694.87200000000007</v>
-      </c>
-      <c r="BO6" s="69">
-        <v>469.23099999999999</v>
-      </c>
-      <c r="BP6" s="69">
-        <v>482.05100000000004</v>
-      </c>
-      <c r="BQ6" s="69">
-        <v>500</v>
-      </c>
-      <c r="BR6" s="69">
-        <v>530.76900000000001</v>
-      </c>
-      <c r="BS6" s="69">
-        <v>553.846</v>
-      </c>
-      <c r="BT6" s="69">
-        <v>566.66700000000003</v>
-      </c>
-      <c r="BU6" s="69">
-        <v>561.53800000000001</v>
-      </c>
-      <c r="BV6" s="69">
-        <v>538.46199999999999</v>
-      </c>
-      <c r="BW6" s="69">
-        <v>512.82100000000003</v>
-      </c>
-      <c r="BX6" s="69">
-        <v>500</v>
-      </c>
-      <c r="BY6" s="69">
-        <v>479.48700000000002</v>
-      </c>
-      <c r="BZ6" s="69">
-        <v>297.43600000000004</v>
-      </c>
-      <c r="CA6" s="69">
-        <v>297.43600000000004</v>
-      </c>
-      <c r="CB6" s="69">
-        <v>312.82100000000003</v>
-      </c>
-      <c r="CC6" s="69">
-        <v>579.48700000000008</v>
-      </c>
-      <c r="CD6" s="69">
-        <v>617.94899999999996</v>
-      </c>
-      <c r="CE6" s="69">
-        <v>648.71799999999996</v>
-      </c>
-      <c r="CF6" s="69">
-        <v>684.61500000000001</v>
-      </c>
-      <c r="CG6" s="69">
-        <v>707.69200000000001</v>
-      </c>
-      <c r="CH6" s="69">
-        <v>720.51299999999992</v>
-      </c>
-      <c r="CI6" s="69">
-        <v>738.46199999999999</v>
-      </c>
-      <c r="CJ6" s="69">
-        <v>751.28200000000004</v>
-      </c>
-      <c r="CK6" s="69">
-        <v>766.66700000000003</v>
-      </c>
-      <c r="CL6" s="69">
-        <v>776.923</v>
-      </c>
-      <c r="CM6" s="69">
-        <v>797.43600000000004</v>
-      </c>
-      <c r="CN6" s="69">
-        <v>817.94899999999996</v>
-      </c>
-      <c r="CO6" s="69">
-        <v>833.33299999999997</v>
-      </c>
-      <c r="CP6" s="69">
-        <v>851.28200000000004</v>
-      </c>
-      <c r="CQ6" s="69">
-        <v>864.10300000000007</v>
-      </c>
-      <c r="CR6" s="69">
-        <v>879.48700000000008</v>
-      </c>
-      <c r="CS6" s="69">
-        <v>894.87200000000007</v>
-      </c>
-      <c r="CT6" s="69">
-        <v>933.33299999999997</v>
-      </c>
-      <c r="CU6" s="69">
-        <v>953.846</v>
-      </c>
-      <c r="CV6" s="69">
-        <v>982.05100000000004</v>
-      </c>
-      <c r="CW6" s="69">
-        <v>566.66700000000003</v>
-      </c>
-      <c r="CX6" s="69">
-        <v>592.30799999999999</v>
-      </c>
-      <c r="CY6" s="69">
-        <v>607.69200000000001</v>
-      </c>
-      <c r="CZ6" s="69">
-        <v>630.76900000000001</v>
-      </c>
-      <c r="DA6" s="69">
-        <v>641.02599999999995</v>
-      </c>
-      <c r="DB6" s="69">
-        <v>643.58999999999992</v>
-      </c>
-      <c r="DC6" s="69">
-        <v>743.58999999999992</v>
-      </c>
-      <c r="DD6" s="69">
-        <v>712.82100000000003</v>
-      </c>
-      <c r="DE6" s="69">
-        <v>679.48700000000008</v>
-      </c>
-      <c r="DF6" s="69">
-        <v>658.97400000000005</v>
-      </c>
-      <c r="DG6" s="69">
-        <v>630.76900000000001</v>
-      </c>
-      <c r="DH6" s="69">
-        <v>612.82100000000003</v>
-      </c>
-      <c r="DI6" s="69">
-        <v>587.17899999999997</v>
-      </c>
-      <c r="DJ6" s="69">
-        <v>551.28200000000004</v>
-      </c>
-      <c r="DK6" s="69">
-        <v>523.077</v>
-      </c>
-      <c r="DL6" s="69">
-        <v>497.43600000000004</v>
-      </c>
-      <c r="DM6" s="69">
-        <v>474.35899999999998</v>
-      </c>
-      <c r="DN6" s="69">
-        <v>448.71800000000002</v>
-      </c>
-      <c r="DO6" s="69">
-        <v>487.17899999999997</v>
-      </c>
-      <c r="DP6" s="69">
-        <v>512.82100000000003</v>
-      </c>
-      <c r="DQ6" s="69">
-        <v>541.02600000000007</v>
-      </c>
-      <c r="DR6" s="69">
-        <v>561.53800000000001</v>
-      </c>
-      <c r="DS6" s="69">
-        <v>520.51299999999992</v>
-      </c>
-      <c r="DT6" s="69">
-        <v>487.17899999999997</v>
-      </c>
-      <c r="DU6" s="69">
-        <v>471.79499999999996</v>
-      </c>
-      <c r="DV6" s="69">
-        <v>461.53799999999995</v>
-      </c>
-      <c r="DW6" s="69">
-        <v>505.12799999999999</v>
-      </c>
-      <c r="DX6" s="69">
-        <v>538.46199999999999</v>
-      </c>
-      <c r="DY6" s="69">
-        <v>574.35899999999992</v>
-      </c>
-      <c r="DZ6" s="69">
-        <v>600</v>
-      </c>
-      <c r="EA6" s="69">
-        <v>641.02599999999995</v>
-      </c>
-      <c r="EB6" s="69">
-        <v>669.23099999999999</v>
-      </c>
-      <c r="EC6" s="69">
-        <v>712.82100000000003</v>
-      </c>
-      <c r="ED6" s="69">
-        <v>743.58999999999992</v>
-      </c>
-      <c r="EE6" s="69">
-        <v>782.05100000000004</v>
-      </c>
-      <c r="EF6" s="69">
-        <v>679.48700000000008</v>
-      </c>
-      <c r="EG6" s="69">
-        <v>684.61500000000001</v>
-      </c>
-      <c r="EH6" s="69">
-        <v>682.05100000000004</v>
-      </c>
-      <c r="EI6" s="69">
-        <v>376.923</v>
-      </c>
-      <c r="EJ6" s="69">
-        <v>394.87200000000001</v>
-      </c>
-      <c r="EK6" s="69">
-        <v>912.82100000000003</v>
-      </c>
-      <c r="EL6" s="69">
-        <v>500</v>
-      </c>
-      <c r="EM6" s="69">
-        <v>479.48700000000002</v>
-      </c>
-      <c r="EN6" s="69">
-        <v>441.02600000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="2:144" x14ac:dyDescent="0.2">
-      <c r="B7" s="68" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="69">
-        <v>971.79500000000007</v>
-      </c>
-      <c r="D7" s="69">
-        <v>960.25599999999997</v>
-      </c>
-      <c r="E7" s="69">
-        <v>944.87200000000007</v>
-      </c>
-      <c r="F7" s="69">
-        <v>914.10300000000007</v>
-      </c>
-      <c r="G7" s="69">
-        <v>883.33299999999997</v>
-      </c>
-      <c r="H7" s="69">
-        <v>848.71799999999996</v>
-      </c>
-      <c r="I7" s="69">
-        <v>798.71799999999996</v>
-      </c>
-      <c r="J7" s="69">
-        <v>775.64099999999996</v>
-      </c>
-      <c r="K7" s="69">
-        <v>744.87200000000007</v>
-      </c>
-      <c r="L7" s="69">
-        <v>714.10300000000007</v>
-      </c>
-      <c r="M7" s="69">
-        <v>664.10300000000007</v>
-      </c>
-      <c r="N7" s="69">
-        <v>617.94899999999996</v>
-      </c>
-      <c r="O7" s="69">
-        <v>571.79499999999996</v>
-      </c>
-      <c r="P7" s="69">
-        <v>529.48700000000008</v>
-      </c>
-      <c r="Q7" s="69">
-        <v>510.25599999999997</v>
-      </c>
-      <c r="R7" s="69">
-        <v>510.25599999999997</v>
-      </c>
-      <c r="S7" s="69">
-        <v>510.25599999999997</v>
-      </c>
-      <c r="T7" s="69">
-        <v>514.10299999999995</v>
-      </c>
-      <c r="U7" s="69">
-        <v>514.10299999999995</v>
-      </c>
-      <c r="V7" s="69">
-        <v>529.48700000000008</v>
-      </c>
-      <c r="W7" s="69">
-        <v>541.02600000000007</v>
-      </c>
-      <c r="X7" s="69">
-        <v>552.56399999999996</v>
-      </c>
-      <c r="Y7" s="69">
-        <v>556.41</v>
-      </c>
-      <c r="Z7" s="69">
-        <v>560.25599999999997</v>
-      </c>
-      <c r="AA7" s="69">
-        <v>579.48700000000008</v>
-      </c>
-      <c r="AB7" s="69">
-        <v>621.79499999999996</v>
-      </c>
-      <c r="AC7" s="69">
-        <v>664.10300000000007</v>
-      </c>
-      <c r="AD7" s="69">
-        <v>691.02599999999995</v>
-      </c>
-      <c r="AE7" s="69">
-        <v>552.56399999999996</v>
-      </c>
-      <c r="AF7" s="69">
-        <v>498.71800000000002</v>
-      </c>
-      <c r="AG7" s="69">
-        <v>460.25599999999997</v>
-      </c>
-      <c r="AH7" s="69">
-        <v>383.33300000000003</v>
-      </c>
-      <c r="AI7" s="69">
-        <v>421.79499999999996</v>
-      </c>
-      <c r="AJ7" s="69">
-        <v>441.02600000000001</v>
-      </c>
-      <c r="AK7" s="69">
-        <v>364.10300000000001</v>
-      </c>
-      <c r="AL7" s="69">
-        <v>325.64100000000002</v>
-      </c>
-      <c r="AM7" s="69">
-        <v>314.10300000000001</v>
-      </c>
-      <c r="AN7" s="69">
-        <v>302.56399999999996</v>
-      </c>
-      <c r="AO7" s="69">
-        <v>321.79499999999996</v>
-      </c>
-      <c r="AP7" s="69">
-        <v>367.94899999999996</v>
-      </c>
-      <c r="AQ7" s="69">
-        <v>414.10300000000001</v>
-      </c>
-      <c r="AR7" s="69">
-        <v>456.40999999999997</v>
-      </c>
-      <c r="AS7" s="69">
-        <v>491.02600000000001</v>
-      </c>
-      <c r="AT7" s="69">
-        <v>360.25599999999997</v>
-      </c>
-      <c r="AU7" s="69">
-        <v>321.79499999999996</v>
-      </c>
-      <c r="AV7" s="69">
-        <v>291.02600000000001</v>
-      </c>
-      <c r="AW7" s="69">
-        <v>267.94899999999996</v>
-      </c>
-      <c r="AX7" s="69">
-        <v>252.56399999999999</v>
-      </c>
-      <c r="AY7" s="69">
-        <v>252.56399999999999</v>
-      </c>
-      <c r="AZ7" s="69">
-        <v>256.40999999999997</v>
-      </c>
-      <c r="BA7" s="69">
-        <v>287.18</v>
-      </c>
-      <c r="BB7" s="69">
-        <v>314.10300000000001</v>
-      </c>
-      <c r="BC7" s="69">
-        <v>348.71800000000002</v>
-      </c>
-      <c r="BD7" s="69">
-        <v>375.64100000000002</v>
-      </c>
-      <c r="BE7" s="69">
-        <v>406.40999999999997</v>
-      </c>
-      <c r="BF7" s="69">
-        <v>421.79499999999996</v>
-      </c>
-      <c r="BG7" s="69">
-        <v>444.87200000000001</v>
-      </c>
-      <c r="BH7" s="69">
-        <v>460.25599999999997</v>
-      </c>
-      <c r="BI7" s="69">
-        <v>467.94899999999996</v>
-      </c>
-      <c r="BJ7" s="69">
-        <v>479.48700000000002</v>
-      </c>
-      <c r="BK7" s="69">
-        <v>537.18000000000006</v>
-      </c>
-      <c r="BL7" s="69">
-        <v>606.41</v>
-      </c>
-      <c r="BM7" s="69">
-        <v>644.87200000000007</v>
-      </c>
-      <c r="BN7" s="69">
-        <v>694.87200000000007</v>
-      </c>
-      <c r="BO7" s="69">
-        <v>798.71799999999996</v>
-      </c>
-      <c r="BP7" s="69">
-        <v>841.02599999999995</v>
-      </c>
-      <c r="BQ7" s="69">
-        <v>852.56399999999996</v>
-      </c>
-      <c r="BR7" s="69">
-        <v>852.56399999999996</v>
-      </c>
-      <c r="BS7" s="69">
-        <v>860.25599999999997</v>
-      </c>
-      <c r="BT7" s="69">
-        <v>860.25599999999997</v>
-      </c>
-      <c r="BU7" s="69">
-        <v>829.48700000000008</v>
-      </c>
-      <c r="BV7" s="69">
-        <v>806.41000000000008</v>
-      </c>
-      <c r="BW7" s="69">
-        <v>787.18000000000006</v>
-      </c>
-      <c r="BX7" s="69">
-        <v>787.18000000000006</v>
-      </c>
-      <c r="BY7" s="69">
-        <v>775.64099999999996</v>
-      </c>
-      <c r="BZ7" s="69">
-        <v>598.71799999999996</v>
-      </c>
-      <c r="CA7" s="69">
-        <v>621.79499999999996</v>
-      </c>
-      <c r="CB7" s="69">
-        <v>625.64100000000008</v>
-      </c>
-      <c r="CC7" s="69">
-        <v>994.87200000000007</v>
-      </c>
-      <c r="CD7" s="69">
-        <v>991.02599999999995</v>
-      </c>
-      <c r="CE7" s="69">
-        <v>975.64099999999996</v>
-      </c>
-      <c r="CF7" s="69">
-        <v>941.02599999999995</v>
-      </c>
-      <c r="CG7" s="69">
-        <v>910.25599999999997</v>
-      </c>
-      <c r="CH7" s="69">
-        <v>864.10300000000007</v>
-      </c>
-      <c r="CI7" s="69">
-        <v>833.33299999999997</v>
-      </c>
-      <c r="CJ7" s="69">
-        <v>791.02599999999995</v>
-      </c>
-      <c r="CK7" s="69">
-        <v>752.56399999999996</v>
-      </c>
-      <c r="CL7" s="69">
-        <v>714.10300000000007</v>
-      </c>
-      <c r="CM7" s="69">
-        <v>667.94899999999996</v>
-      </c>
-      <c r="CN7" s="69">
-        <v>602.56399999999996</v>
-      </c>
-      <c r="CO7" s="69">
-        <v>552.56399999999996</v>
-      </c>
-      <c r="CP7" s="69">
-        <v>514.10299999999995</v>
-      </c>
-      <c r="CQ7" s="69">
-        <v>475.64100000000002</v>
-      </c>
-      <c r="CR7" s="69">
-        <v>460.25599999999997</v>
-      </c>
-      <c r="CS7" s="69">
-        <v>425.64100000000002</v>
-      </c>
-      <c r="CT7" s="69">
-        <v>398.71800000000002</v>
-      </c>
-      <c r="CU7" s="69">
-        <v>367.94899999999996</v>
-      </c>
-      <c r="CV7" s="69">
-        <v>337.18000000000006</v>
-      </c>
-      <c r="CW7" s="69">
-        <v>406.40999999999997</v>
-      </c>
-      <c r="CX7" s="69">
-        <v>383.33300000000003</v>
-      </c>
-      <c r="CY7" s="69">
-        <v>337.18000000000006</v>
-      </c>
-      <c r="CZ7" s="69">
-        <v>291.02600000000001</v>
-      </c>
-      <c r="DA7" s="69">
-        <v>252.56399999999999</v>
-      </c>
-      <c r="DB7" s="69">
-        <v>241.02599999999998</v>
-      </c>
-      <c r="DC7" s="69">
-        <v>229.48699999999999</v>
-      </c>
-      <c r="DD7" s="69">
-        <v>229.48699999999999</v>
-      </c>
-      <c r="DE7" s="69">
-        <v>221.79500000000002</v>
-      </c>
-      <c r="DF7" s="69">
-        <v>202.56399999999999</v>
-      </c>
-      <c r="DG7" s="69">
-        <v>191.02599999999998</v>
-      </c>
-      <c r="DH7" s="69">
-        <v>191.02599999999998</v>
-      </c>
-      <c r="DI7" s="69">
-        <v>183.33300000000003</v>
-      </c>
-      <c r="DJ7" s="69">
-        <v>183.33300000000003</v>
-      </c>
-      <c r="DK7" s="69">
-        <v>183.33300000000003</v>
-      </c>
-      <c r="DL7" s="69">
-        <v>175.64099999999999</v>
-      </c>
-      <c r="DM7" s="69">
-        <v>160.256</v>
-      </c>
-      <c r="DN7" s="69">
-        <v>137.18</v>
-      </c>
-      <c r="DO7" s="69">
-        <v>148.71800000000002</v>
-      </c>
-      <c r="DP7" s="69">
-        <v>148.71800000000002</v>
-      </c>
-      <c r="DQ7" s="69">
-        <v>148.71800000000002</v>
-      </c>
-      <c r="DR7" s="69">
-        <v>141.02600000000001</v>
-      </c>
-      <c r="DS7" s="69">
-        <v>125.64099999999999</v>
-      </c>
-      <c r="DT7" s="69">
-        <v>110.256</v>
-      </c>
-      <c r="DU7" s="69">
-        <v>98.718000000000004</v>
-      </c>
-      <c r="DV7" s="69">
-        <v>60.256</v>
-      </c>
-      <c r="DW7" s="69">
-        <v>94.872</v>
-      </c>
-      <c r="DX7" s="69">
-        <v>102.56399999999999</v>
-      </c>
-      <c r="DY7" s="69">
-        <v>102.56399999999999</v>
-      </c>
-      <c r="DZ7" s="69">
-        <v>106.41</v>
-      </c>
-      <c r="EA7" s="69">
-        <v>106.41</v>
-      </c>
-      <c r="EB7" s="69">
-        <v>106.41</v>
-      </c>
-      <c r="EC7" s="69">
-        <v>106.41</v>
-      </c>
-      <c r="ED7" s="69">
-        <v>106.41</v>
-      </c>
-      <c r="EE7" s="69">
-        <v>106.41</v>
-      </c>
-      <c r="EF7" s="69">
-        <v>87.18</v>
-      </c>
-      <c r="EG7" s="69">
-        <v>52.564</v>
-      </c>
-      <c r="EH7" s="69">
-        <v>29.487000000000002</v>
-      </c>
-      <c r="EI7" s="69">
-        <v>257.69200000000001</v>
-      </c>
-      <c r="EJ7" s="69">
-        <v>253.846</v>
-      </c>
-      <c r="EK7" s="69">
-        <v>415.38499999999999</v>
-      </c>
-      <c r="EL7" s="69">
-        <v>957.69200000000001</v>
-      </c>
-      <c r="EM7" s="69">
-        <v>950</v>
-      </c>
-      <c r="EN7" s="69">
-        <v>926.923</v>
-      </c>
-    </row>
-    <row r="9" spans="2:144" x14ac:dyDescent="0.2">
-      <c r="B9" s="67"/>
-      <c r="C9" s="39"/>
-    </row>
-    <row r="10" spans="2:144" ht="50.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="2:144" x14ac:dyDescent="0.2">
-      <c r="B11" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="39">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="12" spans="2:144" x14ac:dyDescent="0.2">
-      <c r="B12" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="51"/>
-    </row>
-    <row r="14" spans="2:144" x14ac:dyDescent="0.2">
-      <c r="B14" s="67" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="53"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="67" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="70" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="54"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="70" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="54"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="67" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="70" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="55"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B23" s="70" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="55"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C24" s="56"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B25" s="67" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="56"/>
-      <c r="B26" s="70" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="55"/>
-      <c r="G26" s="56"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="56"/>
-      <c r="B27" s="70" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="55"/>
-      <c r="G27" s="56"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B29" s="67" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="56"/>
-      <c r="B30" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="57"/>
-      <c r="G30" s="56"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="56"/>
-      <c r="B31" s="70" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="58"/>
-      <c r="G31" s="56"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C32" s="59"/>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B33" s="70" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" s="55"/>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B34" s="72" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" s="60"/>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B36" s="67" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B37" s="70" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" s="58"/>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B38" s="70" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" s="58"/>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C39" s="59"/>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B40" s="70" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" s="55"/>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B41" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="58"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DDC3AEC-31E5-42A5-B4C0-CF20B03AB1B6}">
-  <dimension ref="A2:EN43"/>
+  <dimension ref="A2:EN41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.6640625" style="52" customWidth="1"/>
@@ -17430,180 +14236,1562 @@
       <c r="C9" s="39"/>
     </row>
     <row r="11" spans="2:144" x14ac:dyDescent="0.2">
-      <c r="B11" s="73"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="75"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="39"/>
     </row>
     <row r="12" spans="2:144" x14ac:dyDescent="0.2">
-      <c r="B12" s="73"/>
-      <c r="C12" s="76"/>
-      <c r="D12" s="75"/>
-    </row>
-    <row r="13" spans="2:144" x14ac:dyDescent="0.2">
-      <c r="B13" s="75"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="59"/>
     </row>
     <row r="14" spans="2:144" x14ac:dyDescent="0.2">
-      <c r="B14" s="73"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
-    </row>
-    <row r="15" spans="2:144" x14ac:dyDescent="0.2">
-      <c r="B15" s="75"/>
-      <c r="C15" s="75"/>
-      <c r="D15" s="75"/>
-    </row>
-    <row r="16" spans="2:144" x14ac:dyDescent="0.2">
-      <c r="B16" s="75"/>
-      <c r="C16" s="75"/>
-      <c r="D16" s="75"/>
+      <c r="B14" s="67"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="73"/>
-      <c r="C17" s="75"/>
-      <c r="D17" s="75"/>
+      <c r="B17" s="67"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="75"/>
-      <c r="C18" s="77"/>
-      <c r="D18" s="75"/>
+      <c r="C18" s="73"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="75"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="75"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="75"/>
-      <c r="C20" s="75"/>
-      <c r="D20" s="75"/>
+      <c r="C19" s="73"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="73"/>
-      <c r="C21" s="75"/>
-      <c r="D21" s="75"/>
+      <c r="B21" s="67"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="75"/>
-      <c r="C22" s="78"/>
-      <c r="D22" s="75"/>
+      <c r="C22" s="56"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B23" s="75"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="75"/>
+      <c r="C23" s="56"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="75"/>
-      <c r="C24" s="78"/>
-      <c r="D24" s="75"/>
+      <c r="C24" s="56"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B25" s="73"/>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
+      <c r="B25" s="67"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="56"/>
-      <c r="B26" s="75"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="75"/>
+      <c r="C26" s="56"/>
       <c r="G26" s="56"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="56"/>
-      <c r="B27" s="75"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="75"/>
+      <c r="C27" s="56"/>
       <c r="G27" s="56"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B28" s="75"/>
-      <c r="C28" s="75"/>
-      <c r="D28" s="75"/>
-    </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B29" s="73"/>
-      <c r="C29" s="75"/>
-      <c r="D29" s="75"/>
+      <c r="B29" s="67"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="56"/>
-      <c r="B30" s="75"/>
-      <c r="C30" s="78"/>
-      <c r="D30" s="75"/>
+      <c r="C30" s="56"/>
       <c r="G30" s="56"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="56"/>
-      <c r="B31" s="75"/>
-      <c r="C31" s="76"/>
-      <c r="D31" s="75"/>
+      <c r="C31" s="59"/>
       <c r="G31" s="56"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B32" s="75"/>
-      <c r="C32" s="76"/>
-      <c r="D32" s="75"/>
+      <c r="C32" s="59"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B33" s="75"/>
-      <c r="C33" s="78"/>
-      <c r="D33" s="75"/>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C33" s="56"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B34" s="75"/>
-      <c r="C34" s="76"/>
-      <c r="D34" s="75"/>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C34" s="59"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B35" s="75"/>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B36" s="67"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B36" s="73"/>
-      <c r="C36" s="75"/>
-      <c r="D36" s="75"/>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C37" s="59"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B37" s="75"/>
-      <c r="C37" s="76"/>
-      <c r="D37" s="75"/>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C38" s="59"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B38" s="75"/>
-      <c r="C38" s="76"/>
-      <c r="D38" s="75"/>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C39" s="59"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B39" s="75"/>
-      <c r="C39" s="76"/>
-      <c r="D39" s="75"/>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C40" s="56"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B40" s="75"/>
-      <c r="C40" s="78"/>
-      <c r="D40" s="75"/>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B41" s="75"/>
-      <c r="C41" s="76"/>
-      <c r="D41" s="75"/>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B42" s="75"/>
-      <c r="C42" s="75"/>
-      <c r="D42" s="75"/>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B43" s="75"/>
-      <c r="C43" s="75"/>
-      <c r="D43" s="75"/>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C41" s="59"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02763E32-D334-407F-8BF3-222AB88B5A7C}">
+  <dimension ref="A2:EN41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.1640625" style="52" customWidth="1"/>
+    <col min="2" max="2" width="35.5" style="52" customWidth="1"/>
+    <col min="3" max="144" width="11.6640625" style="52" bestFit="1" customWidth="1"/>
+    <col min="145" max="16384" width="11.1640625" style="52"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:144" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B2" s="64" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="2:144" x14ac:dyDescent="0.2">
+      <c r="B3" s="52" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="2:144" s="67" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="66">
+        <v>46023</v>
+      </c>
+      <c r="D5" s="66">
+        <v>46024</v>
+      </c>
+      <c r="E5" s="66">
+        <v>46025</v>
+      </c>
+      <c r="F5" s="66">
+        <v>46026</v>
+      </c>
+      <c r="G5" s="66">
+        <v>46027</v>
+      </c>
+      <c r="H5" s="66">
+        <v>46028</v>
+      </c>
+      <c r="I5" s="66">
+        <v>46029</v>
+      </c>
+      <c r="J5" s="66">
+        <v>46030</v>
+      </c>
+      <c r="K5" s="66">
+        <v>46031</v>
+      </c>
+      <c r="L5" s="66">
+        <v>46032</v>
+      </c>
+      <c r="M5" s="66">
+        <v>46033</v>
+      </c>
+      <c r="N5" s="66">
+        <v>46034</v>
+      </c>
+      <c r="O5" s="66">
+        <v>46035</v>
+      </c>
+      <c r="P5" s="66">
+        <v>46036</v>
+      </c>
+      <c r="Q5" s="66">
+        <v>46037</v>
+      </c>
+      <c r="R5" s="66">
+        <v>46038</v>
+      </c>
+      <c r="S5" s="66">
+        <v>46039</v>
+      </c>
+      <c r="T5" s="66">
+        <v>46040</v>
+      </c>
+      <c r="U5" s="66">
+        <v>46041</v>
+      </c>
+      <c r="V5" s="66">
+        <v>46042</v>
+      </c>
+      <c r="W5" s="66">
+        <v>46043</v>
+      </c>
+      <c r="X5" s="66">
+        <v>46044</v>
+      </c>
+      <c r="Y5" s="66">
+        <v>46045</v>
+      </c>
+      <c r="Z5" s="66">
+        <v>46046</v>
+      </c>
+      <c r="AA5" s="66">
+        <v>46047</v>
+      </c>
+      <c r="AB5" s="66">
+        <v>46048</v>
+      </c>
+      <c r="AC5" s="66">
+        <v>46049</v>
+      </c>
+      <c r="AD5" s="66">
+        <v>46050</v>
+      </c>
+      <c r="AE5" s="66">
+        <v>46051</v>
+      </c>
+      <c r="AF5" s="66">
+        <v>46052</v>
+      </c>
+      <c r="AG5" s="66">
+        <v>46053</v>
+      </c>
+      <c r="AH5" s="66">
+        <v>46054</v>
+      </c>
+      <c r="AI5" s="66">
+        <v>46055</v>
+      </c>
+      <c r="AJ5" s="66">
+        <v>46056</v>
+      </c>
+      <c r="AK5" s="66">
+        <v>46057</v>
+      </c>
+      <c r="AL5" s="66">
+        <v>46058</v>
+      </c>
+      <c r="AM5" s="66">
+        <v>46059</v>
+      </c>
+      <c r="AN5" s="66">
+        <v>46060</v>
+      </c>
+      <c r="AO5" s="66">
+        <v>46061</v>
+      </c>
+      <c r="AP5" s="66">
+        <v>46062</v>
+      </c>
+      <c r="AQ5" s="66">
+        <v>46063</v>
+      </c>
+      <c r="AR5" s="66">
+        <v>46064</v>
+      </c>
+      <c r="AS5" s="66">
+        <v>46065</v>
+      </c>
+      <c r="AT5" s="66">
+        <v>46066</v>
+      </c>
+      <c r="AU5" s="66">
+        <v>46067</v>
+      </c>
+      <c r="AV5" s="66">
+        <v>46068</v>
+      </c>
+      <c r="AW5" s="66">
+        <v>46069</v>
+      </c>
+      <c r="AX5" s="66">
+        <v>46070</v>
+      </c>
+      <c r="AY5" s="66">
+        <v>46071</v>
+      </c>
+      <c r="AZ5" s="66">
+        <v>46072</v>
+      </c>
+      <c r="BA5" s="66">
+        <v>46073</v>
+      </c>
+      <c r="BB5" s="66">
+        <v>46074</v>
+      </c>
+      <c r="BC5" s="66">
+        <v>46075</v>
+      </c>
+      <c r="BD5" s="66">
+        <v>46076</v>
+      </c>
+      <c r="BE5" s="66">
+        <v>46077</v>
+      </c>
+      <c r="BF5" s="66">
+        <v>46078</v>
+      </c>
+      <c r="BG5" s="66">
+        <v>46079</v>
+      </c>
+      <c r="BH5" s="66">
+        <v>46080</v>
+      </c>
+      <c r="BI5" s="66">
+        <v>46081</v>
+      </c>
+      <c r="BJ5" s="66">
+        <v>46082</v>
+      </c>
+      <c r="BK5" s="66">
+        <v>46083</v>
+      </c>
+      <c r="BL5" s="66">
+        <v>46084</v>
+      </c>
+      <c r="BM5" s="66">
+        <v>46085</v>
+      </c>
+      <c r="BN5" s="66">
+        <v>46086</v>
+      </c>
+      <c r="BO5" s="66">
+        <v>46087</v>
+      </c>
+      <c r="BP5" s="66">
+        <v>46088</v>
+      </c>
+      <c r="BQ5" s="66">
+        <v>46089</v>
+      </c>
+      <c r="BR5" s="66">
+        <v>46090</v>
+      </c>
+      <c r="BS5" s="66">
+        <v>46091</v>
+      </c>
+      <c r="BT5" s="66">
+        <v>46092</v>
+      </c>
+      <c r="BU5" s="66">
+        <v>46093</v>
+      </c>
+      <c r="BV5" s="66">
+        <v>46094</v>
+      </c>
+      <c r="BW5" s="66">
+        <v>46095</v>
+      </c>
+      <c r="BX5" s="66">
+        <v>46096</v>
+      </c>
+      <c r="BY5" s="66">
+        <v>46097</v>
+      </c>
+      <c r="BZ5" s="66">
+        <v>46098</v>
+      </c>
+      <c r="CA5" s="66">
+        <v>46099</v>
+      </c>
+      <c r="CB5" s="66">
+        <v>46100</v>
+      </c>
+      <c r="CC5" s="66">
+        <v>46101</v>
+      </c>
+      <c r="CD5" s="66">
+        <v>46102</v>
+      </c>
+      <c r="CE5" s="66">
+        <v>46103</v>
+      </c>
+      <c r="CF5" s="66">
+        <v>46104</v>
+      </c>
+      <c r="CG5" s="66">
+        <v>46105</v>
+      </c>
+      <c r="CH5" s="66">
+        <v>46106</v>
+      </c>
+      <c r="CI5" s="66">
+        <v>46107</v>
+      </c>
+      <c r="CJ5" s="66">
+        <v>46108</v>
+      </c>
+      <c r="CK5" s="66">
+        <v>46109</v>
+      </c>
+      <c r="CL5" s="66">
+        <v>46110</v>
+      </c>
+      <c r="CM5" s="66">
+        <v>46111</v>
+      </c>
+      <c r="CN5" s="66">
+        <v>46112</v>
+      </c>
+      <c r="CO5" s="66">
+        <v>46113</v>
+      </c>
+      <c r="CP5" s="66">
+        <v>46114</v>
+      </c>
+      <c r="CQ5" s="66">
+        <v>46115</v>
+      </c>
+      <c r="CR5" s="66">
+        <v>46116</v>
+      </c>
+      <c r="CS5" s="66">
+        <v>46117</v>
+      </c>
+      <c r="CT5" s="66">
+        <v>46118</v>
+      </c>
+      <c r="CU5" s="66">
+        <v>46119</v>
+      </c>
+      <c r="CV5" s="66">
+        <v>46120</v>
+      </c>
+      <c r="CW5" s="66">
+        <v>46121</v>
+      </c>
+      <c r="CX5" s="66">
+        <v>46122</v>
+      </c>
+      <c r="CY5" s="66">
+        <v>46123</v>
+      </c>
+      <c r="CZ5" s="66">
+        <v>46124</v>
+      </c>
+      <c r="DA5" s="66">
+        <v>46125</v>
+      </c>
+      <c r="DB5" s="66">
+        <v>46126</v>
+      </c>
+      <c r="DC5" s="66">
+        <v>46127</v>
+      </c>
+      <c r="DD5" s="66">
+        <v>46128</v>
+      </c>
+      <c r="DE5" s="66">
+        <v>46129</v>
+      </c>
+      <c r="DF5" s="66">
+        <v>46130</v>
+      </c>
+      <c r="DG5" s="66">
+        <v>46131</v>
+      </c>
+      <c r="DH5" s="66">
+        <v>46132</v>
+      </c>
+      <c r="DI5" s="66">
+        <v>46133</v>
+      </c>
+      <c r="DJ5" s="66">
+        <v>46134</v>
+      </c>
+      <c r="DK5" s="66">
+        <v>46135</v>
+      </c>
+      <c r="DL5" s="66">
+        <v>46136</v>
+      </c>
+      <c r="DM5" s="66">
+        <v>46137</v>
+      </c>
+      <c r="DN5" s="66">
+        <v>46138</v>
+      </c>
+      <c r="DO5" s="66">
+        <v>46139</v>
+      </c>
+      <c r="DP5" s="66">
+        <v>46140</v>
+      </c>
+      <c r="DQ5" s="66">
+        <v>46141</v>
+      </c>
+      <c r="DR5" s="66">
+        <v>46142</v>
+      </c>
+      <c r="DS5" s="66">
+        <v>46143</v>
+      </c>
+      <c r="DT5" s="66">
+        <v>46144</v>
+      </c>
+      <c r="DU5" s="66">
+        <v>46145</v>
+      </c>
+      <c r="DV5" s="66">
+        <v>46146</v>
+      </c>
+      <c r="DW5" s="66">
+        <v>46147</v>
+      </c>
+      <c r="DX5" s="66">
+        <v>46148</v>
+      </c>
+      <c r="DY5" s="66">
+        <v>46149</v>
+      </c>
+      <c r="DZ5" s="66">
+        <v>46150</v>
+      </c>
+      <c r="EA5" s="66">
+        <v>46151</v>
+      </c>
+      <c r="EB5" s="66">
+        <v>46152</v>
+      </c>
+      <c r="EC5" s="66">
+        <v>46153</v>
+      </c>
+      <c r="ED5" s="66">
+        <v>46154</v>
+      </c>
+      <c r="EE5" s="66">
+        <v>46155</v>
+      </c>
+      <c r="EF5" s="66">
+        <v>46156</v>
+      </c>
+      <c r="EG5" s="66">
+        <v>46157</v>
+      </c>
+      <c r="EH5" s="66">
+        <v>46158</v>
+      </c>
+      <c r="EI5" s="66">
+        <v>46159</v>
+      </c>
+      <c r="EJ5" s="66">
+        <v>46160</v>
+      </c>
+      <c r="EK5" s="66">
+        <v>46161</v>
+      </c>
+      <c r="EL5" s="66">
+        <v>46162</v>
+      </c>
+      <c r="EM5" s="66">
+        <v>46163</v>
+      </c>
+      <c r="EN5" s="66">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="6" spans="2:144" x14ac:dyDescent="0.2">
+      <c r="B6" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="69">
+        <v>553.846</v>
+      </c>
+      <c r="D6" s="69">
+        <v>515.38499999999999</v>
+      </c>
+      <c r="E6" s="69">
+        <v>461.53799999999995</v>
+      </c>
+      <c r="F6" s="69">
+        <v>428.20500000000004</v>
+      </c>
+      <c r="G6" s="69">
+        <v>407.69200000000001</v>
+      </c>
+      <c r="H6" s="69">
+        <v>387.17899999999997</v>
+      </c>
+      <c r="I6" s="69">
+        <v>356.40999999999997</v>
+      </c>
+      <c r="J6" s="69">
+        <v>330.76900000000001</v>
+      </c>
+      <c r="K6" s="69">
+        <v>289.74399999999997</v>
+      </c>
+      <c r="L6" s="69">
+        <v>261.53800000000001</v>
+      </c>
+      <c r="M6" s="69">
+        <v>230.76899999999998</v>
+      </c>
+      <c r="N6" s="69">
+        <v>223.077</v>
+      </c>
+      <c r="O6" s="69">
+        <v>223.077</v>
+      </c>
+      <c r="P6" s="69">
+        <v>233.33300000000003</v>
+      </c>
+      <c r="Q6" s="69">
+        <v>258.97399999999999</v>
+      </c>
+      <c r="R6" s="69">
+        <v>294.87200000000001</v>
+      </c>
+      <c r="S6" s="69">
+        <v>328.20500000000004</v>
+      </c>
+      <c r="T6" s="69">
+        <v>353.846</v>
+      </c>
+      <c r="U6" s="69">
+        <v>402.56399999999996</v>
+      </c>
+      <c r="V6" s="69">
+        <v>441.02600000000001</v>
+      </c>
+      <c r="W6" s="69">
+        <v>466.66699999999997</v>
+      </c>
+      <c r="X6" s="69">
+        <v>500</v>
+      </c>
+      <c r="Y6" s="69">
+        <v>530.76900000000001</v>
+      </c>
+      <c r="Z6" s="69">
+        <v>566.66700000000003</v>
+      </c>
+      <c r="AA6" s="69">
+        <v>592.30799999999999</v>
+      </c>
+      <c r="AB6" s="69">
+        <v>612.82100000000003</v>
+      </c>
+      <c r="AC6" s="69">
+        <v>615.38499999999999</v>
+      </c>
+      <c r="AD6" s="69">
+        <v>617.94899999999996</v>
+      </c>
+      <c r="AE6" s="69">
+        <v>574.35899999999992</v>
+      </c>
+      <c r="AF6" s="69">
+        <v>548.71799999999996</v>
+      </c>
+      <c r="AG6" s="69">
+        <v>525.64100000000008</v>
+      </c>
+      <c r="AH6" s="69">
+        <v>482.05100000000004</v>
+      </c>
+      <c r="AI6" s="69">
+        <v>494.87200000000001</v>
+      </c>
+      <c r="AJ6" s="69">
+        <v>510.25599999999997</v>
+      </c>
+      <c r="AK6" s="69">
+        <v>453.846</v>
+      </c>
+      <c r="AL6" s="69">
+        <v>428.20500000000004</v>
+      </c>
+      <c r="AM6" s="69">
+        <v>387.17899999999997</v>
+      </c>
+      <c r="AN6" s="69">
+        <v>351.28199999999998</v>
+      </c>
+      <c r="AO6" s="69">
+        <v>325.64100000000002</v>
+      </c>
+      <c r="AP6" s="69">
+        <v>300</v>
+      </c>
+      <c r="AQ6" s="69">
+        <v>335.89699999999999</v>
+      </c>
+      <c r="AR6" s="69">
+        <v>366.66699999999997</v>
+      </c>
+      <c r="AS6" s="69">
+        <v>382.05100000000004</v>
+      </c>
+      <c r="AT6" s="69">
+        <v>297.43600000000004</v>
+      </c>
+      <c r="AU6" s="69">
+        <v>297.43600000000004</v>
+      </c>
+      <c r="AV6" s="69">
+        <v>300</v>
+      </c>
+      <c r="AW6" s="69">
+        <v>320.51299999999998</v>
+      </c>
+      <c r="AX6" s="69">
+        <v>358.97399999999999</v>
+      </c>
+      <c r="AY6" s="69">
+        <v>410.25599999999997</v>
+      </c>
+      <c r="AZ6" s="69">
+        <v>441.02600000000001</v>
+      </c>
+      <c r="BA6" s="69">
+        <v>471.79499999999996</v>
+      </c>
+      <c r="BB6" s="69">
+        <v>494.87200000000001</v>
+      </c>
+      <c r="BC6" s="69">
+        <v>515.38499999999999</v>
+      </c>
+      <c r="BD6" s="69">
+        <v>535.89700000000005</v>
+      </c>
+      <c r="BE6" s="69">
+        <v>551.28200000000004</v>
+      </c>
+      <c r="BF6" s="69">
+        <v>566.66700000000003</v>
+      </c>
+      <c r="BG6" s="69">
+        <v>592.30799999999999</v>
+      </c>
+      <c r="BH6" s="69">
+        <v>623.077</v>
+      </c>
+      <c r="BI6" s="69">
+        <v>648.71799999999996</v>
+      </c>
+      <c r="BJ6" s="69">
+        <v>679.48700000000008</v>
+      </c>
+      <c r="BK6" s="69">
+        <v>705.12799999999993</v>
+      </c>
+      <c r="BL6" s="69">
+        <v>715.38499999999999</v>
+      </c>
+      <c r="BM6" s="69">
+        <v>715.38499999999999</v>
+      </c>
+      <c r="BN6" s="69">
+        <v>694.87200000000007</v>
+      </c>
+      <c r="BO6" s="69">
+        <v>469.23099999999999</v>
+      </c>
+      <c r="BP6" s="69">
+        <v>482.05100000000004</v>
+      </c>
+      <c r="BQ6" s="69">
+        <v>500</v>
+      </c>
+      <c r="BR6" s="69">
+        <v>530.76900000000001</v>
+      </c>
+      <c r="BS6" s="69">
+        <v>553.846</v>
+      </c>
+      <c r="BT6" s="69">
+        <v>566.66700000000003</v>
+      </c>
+      <c r="BU6" s="69">
+        <v>561.53800000000001</v>
+      </c>
+      <c r="BV6" s="69">
+        <v>538.46199999999999</v>
+      </c>
+      <c r="BW6" s="69">
+        <v>512.82100000000003</v>
+      </c>
+      <c r="BX6" s="69">
+        <v>500</v>
+      </c>
+      <c r="BY6" s="69">
+        <v>479.48700000000002</v>
+      </c>
+      <c r="BZ6" s="69">
+        <v>297.43600000000004</v>
+      </c>
+      <c r="CA6" s="69">
+        <v>297.43600000000004</v>
+      </c>
+      <c r="CB6" s="69">
+        <v>312.82100000000003</v>
+      </c>
+      <c r="CC6" s="69">
+        <v>579.48700000000008</v>
+      </c>
+      <c r="CD6" s="69">
+        <v>617.94899999999996</v>
+      </c>
+      <c r="CE6" s="69">
+        <v>648.71799999999996</v>
+      </c>
+      <c r="CF6" s="69">
+        <v>684.61500000000001</v>
+      </c>
+      <c r="CG6" s="69">
+        <v>707.69200000000001</v>
+      </c>
+      <c r="CH6" s="69">
+        <v>720.51299999999992</v>
+      </c>
+      <c r="CI6" s="69">
+        <v>738.46199999999999</v>
+      </c>
+      <c r="CJ6" s="69">
+        <v>751.28200000000004</v>
+      </c>
+      <c r="CK6" s="69">
+        <v>766.66700000000003</v>
+      </c>
+      <c r="CL6" s="69">
+        <v>776.923</v>
+      </c>
+      <c r="CM6" s="69">
+        <v>797.43600000000004</v>
+      </c>
+      <c r="CN6" s="69">
+        <v>817.94899999999996</v>
+      </c>
+      <c r="CO6" s="69">
+        <v>833.33299999999997</v>
+      </c>
+      <c r="CP6" s="69">
+        <v>851.28200000000004</v>
+      </c>
+      <c r="CQ6" s="69">
+        <v>864.10300000000007</v>
+      </c>
+      <c r="CR6" s="69">
+        <v>879.48700000000008</v>
+      </c>
+      <c r="CS6" s="69">
+        <v>894.87200000000007</v>
+      </c>
+      <c r="CT6" s="69">
+        <v>933.33299999999997</v>
+      </c>
+      <c r="CU6" s="69">
+        <v>953.846</v>
+      </c>
+      <c r="CV6" s="69">
+        <v>982.05100000000004</v>
+      </c>
+      <c r="CW6" s="69">
+        <v>566.66700000000003</v>
+      </c>
+      <c r="CX6" s="69">
+        <v>592.30799999999999</v>
+      </c>
+      <c r="CY6" s="69">
+        <v>607.69200000000001</v>
+      </c>
+      <c r="CZ6" s="69">
+        <v>630.76900000000001</v>
+      </c>
+      <c r="DA6" s="69">
+        <v>641.02599999999995</v>
+      </c>
+      <c r="DB6" s="69">
+        <v>643.58999999999992</v>
+      </c>
+      <c r="DC6" s="69">
+        <v>743.58999999999992</v>
+      </c>
+      <c r="DD6" s="69">
+        <v>712.82100000000003</v>
+      </c>
+      <c r="DE6" s="69">
+        <v>679.48700000000008</v>
+      </c>
+      <c r="DF6" s="69">
+        <v>658.97400000000005</v>
+      </c>
+      <c r="DG6" s="69">
+        <v>630.76900000000001</v>
+      </c>
+      <c r="DH6" s="69">
+        <v>612.82100000000003</v>
+      </c>
+      <c r="DI6" s="69">
+        <v>587.17899999999997</v>
+      </c>
+      <c r="DJ6" s="69">
+        <v>551.28200000000004</v>
+      </c>
+      <c r="DK6" s="69">
+        <v>523.077</v>
+      </c>
+      <c r="DL6" s="69">
+        <v>497.43600000000004</v>
+      </c>
+      <c r="DM6" s="69">
+        <v>474.35899999999998</v>
+      </c>
+      <c r="DN6" s="69">
+        <v>448.71800000000002</v>
+      </c>
+      <c r="DO6" s="69">
+        <v>487.17899999999997</v>
+      </c>
+      <c r="DP6" s="69">
+        <v>512.82100000000003</v>
+      </c>
+      <c r="DQ6" s="69">
+        <v>541.02600000000007</v>
+      </c>
+      <c r="DR6" s="69">
+        <v>561.53800000000001</v>
+      </c>
+      <c r="DS6" s="69">
+        <v>520.51299999999992</v>
+      </c>
+      <c r="DT6" s="69">
+        <v>487.17899999999997</v>
+      </c>
+      <c r="DU6" s="69">
+        <v>471.79499999999996</v>
+      </c>
+      <c r="DV6" s="69">
+        <v>461.53799999999995</v>
+      </c>
+      <c r="DW6" s="69">
+        <v>505.12799999999999</v>
+      </c>
+      <c r="DX6" s="69">
+        <v>538.46199999999999</v>
+      </c>
+      <c r="DY6" s="69">
+        <v>574.35899999999992</v>
+      </c>
+      <c r="DZ6" s="69">
+        <v>600</v>
+      </c>
+      <c r="EA6" s="69">
+        <v>641.02599999999995</v>
+      </c>
+      <c r="EB6" s="69">
+        <v>669.23099999999999</v>
+      </c>
+      <c r="EC6" s="69">
+        <v>712.82100000000003</v>
+      </c>
+      <c r="ED6" s="69">
+        <v>743.58999999999992</v>
+      </c>
+      <c r="EE6" s="69">
+        <v>782.05100000000004</v>
+      </c>
+      <c r="EF6" s="69">
+        <v>679.48700000000008</v>
+      </c>
+      <c r="EG6" s="69">
+        <v>684.61500000000001</v>
+      </c>
+      <c r="EH6" s="69">
+        <v>682.05100000000004</v>
+      </c>
+      <c r="EI6" s="69">
+        <v>376.923</v>
+      </c>
+      <c r="EJ6" s="69">
+        <v>394.87200000000001</v>
+      </c>
+      <c r="EK6" s="69">
+        <v>912.82100000000003</v>
+      </c>
+      <c r="EL6" s="69">
+        <v>500</v>
+      </c>
+      <c r="EM6" s="69">
+        <v>479.48700000000002</v>
+      </c>
+      <c r="EN6" s="69">
+        <v>441.02600000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="2:144" x14ac:dyDescent="0.2">
+      <c r="B7" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="69">
+        <v>971.79500000000007</v>
+      </c>
+      <c r="D7" s="69">
+        <v>960.25599999999997</v>
+      </c>
+      <c r="E7" s="69">
+        <v>944.87200000000007</v>
+      </c>
+      <c r="F7" s="69">
+        <v>914.10300000000007</v>
+      </c>
+      <c r="G7" s="69">
+        <v>883.33299999999997</v>
+      </c>
+      <c r="H7" s="69">
+        <v>848.71799999999996</v>
+      </c>
+      <c r="I7" s="69">
+        <v>798.71799999999996</v>
+      </c>
+      <c r="J7" s="69">
+        <v>775.64099999999996</v>
+      </c>
+      <c r="K7" s="69">
+        <v>744.87200000000007</v>
+      </c>
+      <c r="L7" s="69">
+        <v>714.10300000000007</v>
+      </c>
+      <c r="M7" s="69">
+        <v>664.10300000000007</v>
+      </c>
+      <c r="N7" s="69">
+        <v>617.94899999999996</v>
+      </c>
+      <c r="O7" s="69">
+        <v>571.79499999999996</v>
+      </c>
+      <c r="P7" s="69">
+        <v>529.48700000000008</v>
+      </c>
+      <c r="Q7" s="69">
+        <v>510.25599999999997</v>
+      </c>
+      <c r="R7" s="69">
+        <v>510.25599999999997</v>
+      </c>
+      <c r="S7" s="69">
+        <v>510.25599999999997</v>
+      </c>
+      <c r="T7" s="69">
+        <v>514.10299999999995</v>
+      </c>
+      <c r="U7" s="69">
+        <v>514.10299999999995</v>
+      </c>
+      <c r="V7" s="69">
+        <v>529.48700000000008</v>
+      </c>
+      <c r="W7" s="69">
+        <v>541.02600000000007</v>
+      </c>
+      <c r="X7" s="69">
+        <v>552.56399999999996</v>
+      </c>
+      <c r="Y7" s="69">
+        <v>556.41</v>
+      </c>
+      <c r="Z7" s="69">
+        <v>560.25599999999997</v>
+      </c>
+      <c r="AA7" s="69">
+        <v>579.48700000000008</v>
+      </c>
+      <c r="AB7" s="69">
+        <v>621.79499999999996</v>
+      </c>
+      <c r="AC7" s="69">
+        <v>664.10300000000007</v>
+      </c>
+      <c r="AD7" s="69">
+        <v>691.02599999999995</v>
+      </c>
+      <c r="AE7" s="69">
+        <v>552.56399999999996</v>
+      </c>
+      <c r="AF7" s="69">
+        <v>498.71800000000002</v>
+      </c>
+      <c r="AG7" s="69">
+        <v>460.25599999999997</v>
+      </c>
+      <c r="AH7" s="69">
+        <v>383.33300000000003</v>
+      </c>
+      <c r="AI7" s="69">
+        <v>421.79499999999996</v>
+      </c>
+      <c r="AJ7" s="69">
+        <v>441.02600000000001</v>
+      </c>
+      <c r="AK7" s="69">
+        <v>364.10300000000001</v>
+      </c>
+      <c r="AL7" s="69">
+        <v>325.64100000000002</v>
+      </c>
+      <c r="AM7" s="69">
+        <v>314.10300000000001</v>
+      </c>
+      <c r="AN7" s="69">
+        <v>302.56399999999996</v>
+      </c>
+      <c r="AO7" s="69">
+        <v>321.79499999999996</v>
+      </c>
+      <c r="AP7" s="69">
+        <v>367.94899999999996</v>
+      </c>
+      <c r="AQ7" s="69">
+        <v>414.10300000000001</v>
+      </c>
+      <c r="AR7" s="69">
+        <v>456.40999999999997</v>
+      </c>
+      <c r="AS7" s="69">
+        <v>491.02600000000001</v>
+      </c>
+      <c r="AT7" s="69">
+        <v>360.25599999999997</v>
+      </c>
+      <c r="AU7" s="69">
+        <v>321.79499999999996</v>
+      </c>
+      <c r="AV7" s="69">
+        <v>291.02600000000001</v>
+      </c>
+      <c r="AW7" s="69">
+        <v>267.94899999999996</v>
+      </c>
+      <c r="AX7" s="69">
+        <v>252.56399999999999</v>
+      </c>
+      <c r="AY7" s="69">
+        <v>252.56399999999999</v>
+      </c>
+      <c r="AZ7" s="69">
+        <v>256.40999999999997</v>
+      </c>
+      <c r="BA7" s="69">
+        <v>287.18</v>
+      </c>
+      <c r="BB7" s="69">
+        <v>314.10300000000001</v>
+      </c>
+      <c r="BC7" s="69">
+        <v>348.71800000000002</v>
+      </c>
+      <c r="BD7" s="69">
+        <v>375.64100000000002</v>
+      </c>
+      <c r="BE7" s="69">
+        <v>406.40999999999997</v>
+      </c>
+      <c r="BF7" s="69">
+        <v>421.79499999999996</v>
+      </c>
+      <c r="BG7" s="69">
+        <v>444.87200000000001</v>
+      </c>
+      <c r="BH7" s="69">
+        <v>460.25599999999997</v>
+      </c>
+      <c r="BI7" s="69">
+        <v>467.94899999999996</v>
+      </c>
+      <c r="BJ7" s="69">
+        <v>479.48700000000002</v>
+      </c>
+      <c r="BK7" s="69">
+        <v>537.18000000000006</v>
+      </c>
+      <c r="BL7" s="69">
+        <v>606.41</v>
+      </c>
+      <c r="BM7" s="69">
+        <v>644.87200000000007</v>
+      </c>
+      <c r="BN7" s="69">
+        <v>694.87200000000007</v>
+      </c>
+      <c r="BO7" s="69">
+        <v>798.71799999999996</v>
+      </c>
+      <c r="BP7" s="69">
+        <v>841.02599999999995</v>
+      </c>
+      <c r="BQ7" s="69">
+        <v>852.56399999999996</v>
+      </c>
+      <c r="BR7" s="69">
+        <v>852.56399999999996</v>
+      </c>
+      <c r="BS7" s="69">
+        <v>860.25599999999997</v>
+      </c>
+      <c r="BT7" s="69">
+        <v>860.25599999999997</v>
+      </c>
+      <c r="BU7" s="69">
+        <v>829.48700000000008</v>
+      </c>
+      <c r="BV7" s="69">
+        <v>806.41000000000008</v>
+      </c>
+      <c r="BW7" s="69">
+        <v>787.18000000000006</v>
+      </c>
+      <c r="BX7" s="69">
+        <v>787.18000000000006</v>
+      </c>
+      <c r="BY7" s="69">
+        <v>775.64099999999996</v>
+      </c>
+      <c r="BZ7" s="69">
+        <v>598.71799999999996</v>
+      </c>
+      <c r="CA7" s="69">
+        <v>621.79499999999996</v>
+      </c>
+      <c r="CB7" s="69">
+        <v>625.64100000000008</v>
+      </c>
+      <c r="CC7" s="69">
+        <v>994.87200000000007</v>
+      </c>
+      <c r="CD7" s="69">
+        <v>991.02599999999995</v>
+      </c>
+      <c r="CE7" s="69">
+        <v>975.64099999999996</v>
+      </c>
+      <c r="CF7" s="69">
+        <v>941.02599999999995</v>
+      </c>
+      <c r="CG7" s="69">
+        <v>910.25599999999997</v>
+      </c>
+      <c r="CH7" s="69">
+        <v>864.10300000000007</v>
+      </c>
+      <c r="CI7" s="69">
+        <v>833.33299999999997</v>
+      </c>
+      <c r="CJ7" s="69">
+        <v>791.02599999999995</v>
+      </c>
+      <c r="CK7" s="69">
+        <v>752.56399999999996</v>
+      </c>
+      <c r="CL7" s="69">
+        <v>714.10300000000007</v>
+      </c>
+      <c r="CM7" s="69">
+        <v>667.94899999999996</v>
+      </c>
+      <c r="CN7" s="69">
+        <v>602.56399999999996</v>
+      </c>
+      <c r="CO7" s="69">
+        <v>552.56399999999996</v>
+      </c>
+      <c r="CP7" s="69">
+        <v>514.10299999999995</v>
+      </c>
+      <c r="CQ7" s="69">
+        <v>475.64100000000002</v>
+      </c>
+      <c r="CR7" s="69">
+        <v>460.25599999999997</v>
+      </c>
+      <c r="CS7" s="69">
+        <v>425.64100000000002</v>
+      </c>
+      <c r="CT7" s="69">
+        <v>398.71800000000002</v>
+      </c>
+      <c r="CU7" s="69">
+        <v>367.94899999999996</v>
+      </c>
+      <c r="CV7" s="69">
+        <v>337.18000000000006</v>
+      </c>
+      <c r="CW7" s="69">
+        <v>406.40999999999997</v>
+      </c>
+      <c r="CX7" s="69">
+        <v>383.33300000000003</v>
+      </c>
+      <c r="CY7" s="69">
+        <v>337.18000000000006</v>
+      </c>
+      <c r="CZ7" s="69">
+        <v>291.02600000000001</v>
+      </c>
+      <c r="DA7" s="69">
+        <v>252.56399999999999</v>
+      </c>
+      <c r="DB7" s="69">
+        <v>241.02599999999998</v>
+      </c>
+      <c r="DC7" s="69">
+        <v>229.48699999999999</v>
+      </c>
+      <c r="DD7" s="69">
+        <v>229.48699999999999</v>
+      </c>
+      <c r="DE7" s="69">
+        <v>221.79500000000002</v>
+      </c>
+      <c r="DF7" s="69">
+        <v>202.56399999999999</v>
+      </c>
+      <c r="DG7" s="69">
+        <v>191.02599999999998</v>
+      </c>
+      <c r="DH7" s="69">
+        <v>191.02599999999998</v>
+      </c>
+      <c r="DI7" s="69">
+        <v>183.33300000000003</v>
+      </c>
+      <c r="DJ7" s="69">
+        <v>183.33300000000003</v>
+      </c>
+      <c r="DK7" s="69">
+        <v>183.33300000000003</v>
+      </c>
+      <c r="DL7" s="69">
+        <v>175.64099999999999</v>
+      </c>
+      <c r="DM7" s="69">
+        <v>160.256</v>
+      </c>
+      <c r="DN7" s="69">
+        <v>137.18</v>
+      </c>
+      <c r="DO7" s="69">
+        <v>148.71800000000002</v>
+      </c>
+      <c r="DP7" s="69">
+        <v>148.71800000000002</v>
+      </c>
+      <c r="DQ7" s="69">
+        <v>148.71800000000002</v>
+      </c>
+      <c r="DR7" s="69">
+        <v>141.02600000000001</v>
+      </c>
+      <c r="DS7" s="69">
+        <v>125.64099999999999</v>
+      </c>
+      <c r="DT7" s="69">
+        <v>110.256</v>
+      </c>
+      <c r="DU7" s="69">
+        <v>98.718000000000004</v>
+      </c>
+      <c r="DV7" s="69">
+        <v>60.256</v>
+      </c>
+      <c r="DW7" s="69">
+        <v>94.872</v>
+      </c>
+      <c r="DX7" s="69">
+        <v>102.56399999999999</v>
+      </c>
+      <c r="DY7" s="69">
+        <v>102.56399999999999</v>
+      </c>
+      <c r="DZ7" s="69">
+        <v>106.41</v>
+      </c>
+      <c r="EA7" s="69">
+        <v>106.41</v>
+      </c>
+      <c r="EB7" s="69">
+        <v>106.41</v>
+      </c>
+      <c r="EC7" s="69">
+        <v>106.41</v>
+      </c>
+      <c r="ED7" s="69">
+        <v>106.41</v>
+      </c>
+      <c r="EE7" s="69">
+        <v>106.41</v>
+      </c>
+      <c r="EF7" s="69">
+        <v>87.18</v>
+      </c>
+      <c r="EG7" s="69">
+        <v>52.564</v>
+      </c>
+      <c r="EH7" s="69">
+        <v>29.487000000000002</v>
+      </c>
+      <c r="EI7" s="69">
+        <v>257.69200000000001</v>
+      </c>
+      <c r="EJ7" s="69">
+        <v>253.846</v>
+      </c>
+      <c r="EK7" s="69">
+        <v>415.38499999999999</v>
+      </c>
+      <c r="EL7" s="69">
+        <v>957.69200000000001</v>
+      </c>
+      <c r="EM7" s="69">
+        <v>950</v>
+      </c>
+      <c r="EN7" s="69">
+        <v>926.923</v>
+      </c>
+    </row>
+    <row r="9" spans="2:144" x14ac:dyDescent="0.2">
+      <c r="B9" s="67"/>
+      <c r="C9" s="39"/>
+    </row>
+    <row r="11" spans="2:144" x14ac:dyDescent="0.2">
+      <c r="B11" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="39">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="12" spans="2:144" x14ac:dyDescent="0.2">
+      <c r="B12" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="51"/>
+    </row>
+    <row r="14" spans="2:144" x14ac:dyDescent="0.2">
+      <c r="B14" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="53"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B17" s="67" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B18" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="54"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B19" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="54"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="67" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B22" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="55"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B23" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="55"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C24" s="56"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B25" s="67" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="56"/>
+      <c r="B26" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="55"/>
+      <c r="G26" s="56"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="56"/>
+      <c r="B27" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="55"/>
+      <c r="G27" s="56"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B29" s="67" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="56"/>
+      <c r="B30" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="57"/>
+      <c r="G30" s="56"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="56"/>
+      <c r="B31" s="70" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="58"/>
+      <c r="G31" s="56"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C32" s="59"/>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B33" s="70" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="55"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B34" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="60"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B36" s="67" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B37" s="70" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="58"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B38" s="70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="58"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C39" s="59"/>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B40" s="70" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="55"/>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B41" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="58"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -24421,10 +22609,14 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A8489F-5371-4F18-B42C-3A166E045C9D}">
-  <dimension ref="C5:AD21"/>
+  <sheetPr>
+    <tabColor theme="8" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="C5:AN22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="18" width="15.6640625" customWidth="1"/>
+    <col min="29" max="29" width="53" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="3:30" x14ac:dyDescent="0.2">
@@ -24599,7 +22791,7 @@
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
     </row>
-    <row r="15" spans="3:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="3:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -24622,7 +22814,9 @@
       <c r="Z15" s="9"/>
       <c r="AA15" s="9"/>
       <c r="AB15" s="9"/>
-      <c r="AC15" s="9"/>
+      <c r="AC15" s="77" t="s">
+        <v>69</v>
+      </c>
       <c r="AD15" s="9"/>
     </row>
     <row r="16" spans="3:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -24651,7 +22845,7 @@
       <c r="AC16" s="9"/>
       <c r="AD16" s="9"/>
     </row>
-    <row r="17" spans="10:30" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="10:40" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N17" s="9"/>
       <c r="O17" s="9"/>
       <c r="P17" s="9"/>
@@ -24669,19 +22863,93 @@
       <c r="AC17" s="9"/>
       <c r="AD17" s="9"/>
     </row>
-    <row r="18" spans="10:30" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="10:40" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J18" s="12"/>
       <c r="K18" s="12"/>
       <c r="L18" s="12"/>
     </row>
-    <row r="19" spans="10:30" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="10:30" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="10:40" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="10:40" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
     </row>
-    <row r="21" spans="10:30" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="10:40" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="10:40" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AC22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE22" s="1"/>
+      <c r="AI22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN22" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E2E4326-CC0C-4587-A5D6-F23562F603B9}">
+  <sheetPr>
+    <tabColor theme="8" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="41" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="76"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="75" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="75" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="75" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I20" s="74"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{69E85E3E-4425-4445-AD41-609E7650CB9B}"/>
+    <hyperlink ref="D6" r:id="rId2" xr:uid="{82164B91-A8BE-4333-9FA4-F388AFE63AC3}"/>
+    <hyperlink ref="D9" r:id="rId3" xr:uid="{29B33E55-0DDE-4826-A44E-F37D2B412D8B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>